--- a/research/traditional_assets/database/data/bulgaria/bulgaria_computer_services.xlsx
+++ b/research/traditional_assets/database/data/bulgaria/bulgaria_computer_services.xlsx
@@ -1400,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1537,22 +1537,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1099440562463375</v>
+        <v>0.1098746121900912</v>
       </c>
       <c r="C2">
-        <v>71.49654329878129</v>
+        <v>70.85501213824615</v>
       </c>
       <c r="D2">
-        <v>67.8965432987813</v>
+        <v>67.95601213824615</v>
       </c>
       <c r="E2">
-        <v>-13.5</v>
+        <v>-12.799</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.701</v>
       </c>
       <c r="G2">
         <v>3.6</v>
@@ -1573,28 +1573,28 @@
         <v>7.12</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.03526029999999999</v>
       </c>
       <c r="N2">
-        <v>7.12</v>
+        <v>7.0847397</v>
       </c>
       <c r="O2">
-        <v>0.7120000000000001</v>
+        <v>0.70847397</v>
       </c>
       <c r="P2">
-        <v>6.408</v>
+        <v>6.37626573</v>
       </c>
       <c r="Q2">
-        <v>7.128</v>
+        <v>7.09626573</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1099440562463375</v>
+        <v>0.1105271840303952</v>
       </c>
       <c r="T2">
-        <v>0.9922881498763956</v>
+        <v>1.001308951238908</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>201.926812874536</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1619,22 +1619,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1098746121900912</v>
+        <v>0.1098051681338449</v>
       </c>
       <c r="C3">
-        <v>70.85501213824615</v>
+        <v>70.21358524349472</v>
       </c>
       <c r="D3">
-        <v>67.95601213824615</v>
+        <v>68.01558524349473</v>
       </c>
       <c r="E3">
-        <v>-12.799</v>
+        <v>-12.098</v>
       </c>
       <c r="F3">
-        <v>0.701</v>
+        <v>1.402</v>
       </c>
       <c r="G3">
         <v>3.6</v>
@@ -1655,28 +1655,28 @@
         <v>7.12</v>
       </c>
       <c r="M3">
-        <v>0.03526029999999999</v>
+        <v>0.07052059999999999</v>
       </c>
       <c r="N3">
-        <v>7.0847397</v>
+        <v>7.0494794</v>
       </c>
       <c r="O3">
-        <v>0.70847397</v>
+        <v>0.7049479400000001</v>
       </c>
       <c r="P3">
-        <v>6.37626573</v>
+        <v>6.34453146</v>
       </c>
       <c r="Q3">
-        <v>7.09626573</v>
+        <v>7.06453146</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1105271840303952</v>
+        <v>0.1111222123814744</v>
       </c>
       <c r="T3">
-        <v>1.001308951238908</v>
+        <v>1.010513850588411</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>201.926812874536</v>
+        <v>100.963406437268</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1701,22 +1701,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1098051681338449</v>
+        <v>0.1097357240775985</v>
       </c>
       <c r="C4">
-        <v>70.21358524349472</v>
+        <v>69.57226288897897</v>
       </c>
       <c r="D4">
-        <v>68.01558524349473</v>
+        <v>68.07526288897897</v>
       </c>
       <c r="E4">
-        <v>-12.098</v>
+        <v>-11.397</v>
       </c>
       <c r="F4">
-        <v>1.402</v>
+        <v>2.103</v>
       </c>
       <c r="G4">
         <v>3.6</v>
@@ -1737,28 +1737,28 @@
         <v>7.12</v>
       </c>
       <c r="M4">
-        <v>0.07052059999999999</v>
+        <v>0.1057809</v>
       </c>
       <c r="N4">
-        <v>7.0494794</v>
+        <v>7.0142191</v>
       </c>
       <c r="O4">
-        <v>0.7049479400000001</v>
+        <v>0.7014219100000001</v>
       </c>
       <c r="P4">
-        <v>6.34453146</v>
+        <v>6.31279719</v>
       </c>
       <c r="Q4">
-        <v>7.06453146</v>
+        <v>7.032797189999999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1111222123814744</v>
+        <v>0.111729509358349</v>
       </c>
       <c r="T4">
-        <v>1.010513850588411</v>
+        <v>1.019908541677079</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>100.963406437268</v>
+        <v>67.30893762484533</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1783,22 +1783,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1097357240775985</v>
+        <v>0.1096662800213522</v>
       </c>
       <c r="C5">
-        <v>69.57226288897897</v>
+        <v>68.9310453501149</v>
       </c>
       <c r="D5">
-        <v>68.07526288897897</v>
+        <v>68.13504535011491</v>
       </c>
       <c r="E5">
-        <v>-11.397</v>
+        <v>-10.696</v>
       </c>
       <c r="F5">
-        <v>2.103</v>
+        <v>2.804</v>
       </c>
       <c r="G5">
         <v>3.6</v>
@@ -1819,28 +1819,28 @@
         <v>7.12</v>
       </c>
       <c r="M5">
-        <v>0.1057809</v>
+        <v>0.1410412</v>
       </c>
       <c r="N5">
-        <v>7.0142191</v>
+        <v>6.9789588</v>
       </c>
       <c r="O5">
-        <v>0.7014219100000001</v>
+        <v>0.69789588</v>
       </c>
       <c r="P5">
-        <v>6.31279719</v>
+        <v>6.28106292</v>
       </c>
       <c r="Q5">
-        <v>7.032797189999999</v>
+        <v>7.00106292</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.111729509358349</v>
+        <v>0.1123494583555752</v>
       </c>
       <c r="T5">
-        <v>1.019908541677079</v>
+        <v>1.02949895549676</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>67.30893762484533</v>
+        <v>50.481703218634</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1865,22 +1865,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1096662800213522</v>
+        <v>0.1095968359651058</v>
       </c>
       <c r="C6">
-        <v>68.9310453501149</v>
+        <v>68.28993290328687</v>
       </c>
       <c r="D6">
-        <v>68.13504535011491</v>
+        <v>68.19493290328687</v>
       </c>
       <c r="E6">
-        <v>-10.696</v>
+        <v>-9.995000000000001</v>
       </c>
       <c r="F6">
-        <v>2.804</v>
+        <v>3.505</v>
       </c>
       <c r="G6">
         <v>3.6</v>
@@ -1901,28 +1901,28 @@
         <v>7.12</v>
       </c>
       <c r="M6">
-        <v>0.1410412</v>
+        <v>0.1763015</v>
       </c>
       <c r="N6">
-        <v>6.9789588</v>
+        <v>6.9436985</v>
       </c>
       <c r="O6">
-        <v>0.69789588</v>
+        <v>0.6943698500000001</v>
       </c>
       <c r="P6">
-        <v>6.28106292</v>
+        <v>6.24932865</v>
       </c>
       <c r="Q6">
-        <v>7.00106292</v>
+        <v>6.96932865</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1123494583555752</v>
+        <v>0.1129824589106377</v>
       </c>
       <c r="T6">
-        <v>1.02949895549676</v>
+        <v>1.039291272765277</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>50.481703218634</v>
+        <v>40.3853625749072</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1947,22 +1947,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1095968359651058</v>
+        <v>0.1095273919088595</v>
       </c>
       <c r="C7">
-        <v>68.28993290328687</v>
+        <v>67.64892582585175</v>
       </c>
       <c r="D7">
-        <v>68.19493290328687</v>
+        <v>68.25492582585176</v>
       </c>
       <c r="E7">
-        <v>-9.995000000000001</v>
+        <v>-9.294</v>
       </c>
       <c r="F7">
-        <v>3.505</v>
+        <v>4.206</v>
       </c>
       <c r="G7">
         <v>3.6</v>
@@ -1983,28 +1983,28 @@
         <v>7.12</v>
       </c>
       <c r="M7">
-        <v>0.1763015</v>
+        <v>0.2115618</v>
       </c>
       <c r="N7">
-        <v>6.9436985</v>
+        <v>6.9084382</v>
       </c>
       <c r="O7">
-        <v>0.6943698500000001</v>
+        <v>0.69084382</v>
       </c>
       <c r="P7">
-        <v>6.24932865</v>
+        <v>6.21759438</v>
       </c>
       <c r="Q7">
-        <v>6.96932865</v>
+        <v>6.937594379999999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1129824589106377</v>
+        <v>0.1136289275626165</v>
       </c>
       <c r="T7">
-        <v>1.039291272765277</v>
+        <v>1.04929193720972</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>40.3853625749072</v>
+        <v>33.65446881242266</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1095273919088595</v>
+        <v>0.1094579478526132</v>
       </c>
       <c r="C8">
-        <v>67.64892582585175</v>
+        <v>67.00802439614327</v>
       </c>
       <c r="D8">
-        <v>68.25492582585176</v>
+        <v>68.31502439614327</v>
       </c>
       <c r="E8">
-        <v>-9.294</v>
+        <v>-8.593</v>
       </c>
       <c r="F8">
-        <v>4.206</v>
+        <v>4.906999999999999</v>
       </c>
       <c r="G8">
         <v>3.6</v>
@@ -2065,28 +2065,28 @@
         <v>7.12</v>
       </c>
       <c r="M8">
-        <v>0.2115618</v>
+        <v>0.2468220999999999</v>
       </c>
       <c r="N8">
-        <v>6.9084382</v>
+        <v>6.8731779</v>
       </c>
       <c r="O8">
-        <v>0.69084382</v>
+        <v>0.68731779</v>
       </c>
       <c r="P8">
-        <v>6.21759438</v>
+        <v>6.18586011</v>
       </c>
       <c r="Q8">
-        <v>6.937594379999999</v>
+        <v>6.90586011</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1136289275626165</v>
+        <v>0.1142892987662507</v>
       </c>
       <c r="T8">
-        <v>1.04929193720972</v>
+        <v>1.059507669706732</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>33.65446881242266</v>
+        <v>28.84668755350514</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2111,22 +2111,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1094579478526132</v>
+        <v>0.1093885037963668</v>
       </c>
       <c r="C9">
-        <v>67.00802439614328</v>
+        <v>66.36722889347641</v>
       </c>
       <c r="D9">
-        <v>68.31502439614329</v>
+        <v>68.37522889347642</v>
       </c>
       <c r="E9">
-        <v>-8.593</v>
+        <v>-7.892</v>
       </c>
       <c r="F9">
-        <v>4.907</v>
+        <v>5.608</v>
       </c>
       <c r="G9">
         <v>3.6</v>
@@ -2147,28 +2147,28 @@
         <v>7.12</v>
       </c>
       <c r="M9">
-        <v>0.2468221</v>
+        <v>0.2820824</v>
       </c>
       <c r="N9">
-        <v>6.8731779</v>
+        <v>6.8379176</v>
       </c>
       <c r="O9">
-        <v>0.68731779</v>
+        <v>0.6837917600000001</v>
       </c>
       <c r="P9">
-        <v>6.18586011</v>
+        <v>6.15412584</v>
       </c>
       <c r="Q9">
-        <v>6.90586011</v>
+        <v>6.87412584</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1142892987662507</v>
+        <v>0.1149640258656161</v>
       </c>
       <c r="T9">
-        <v>1.059507669706732</v>
+        <v>1.069945483344983</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>28.84668755350514</v>
+        <v>25.240851609317</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2193,22 +2193,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1093885037963668</v>
+        <v>0.1093190597401205</v>
       </c>
       <c r="C10">
-        <v>66.36722889347641</v>
+        <v>65.7265395981515</v>
       </c>
       <c r="D10">
-        <v>68.37522889347642</v>
+        <v>68.43553959815151</v>
       </c>
       <c r="E10">
-        <v>-7.892</v>
+        <v>-7.191000000000001</v>
       </c>
       <c r="F10">
-        <v>5.608</v>
+        <v>6.308999999999999</v>
       </c>
       <c r="G10">
         <v>3.6</v>
@@ -2229,28 +2229,28 @@
         <v>7.12</v>
       </c>
       <c r="M10">
-        <v>0.2820824</v>
+        <v>0.3173426999999999</v>
       </c>
       <c r="N10">
-        <v>6.8379176</v>
+        <v>6.8026573</v>
       </c>
       <c r="O10">
-        <v>0.6837917600000001</v>
+        <v>0.68026573</v>
       </c>
       <c r="P10">
-        <v>6.15412584</v>
+        <v>6.12239157</v>
       </c>
       <c r="Q10">
-        <v>6.87412584</v>
+        <v>6.842391569999999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1149640258656161</v>
+        <v>0.1156535821320006</v>
       </c>
       <c r="T10">
-        <v>1.069945483344983</v>
+        <v>1.080612699480778</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>25.240851609317</v>
+        <v>22.43631254161511</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2275,22 +2275,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1093190597401205</v>
+        <v>0.1092496156838742</v>
       </c>
       <c r="C11">
-        <v>65.7265395981515</v>
+        <v>65.0859567914588</v>
       </c>
       <c r="D11">
-        <v>68.43553959815151</v>
+        <v>68.49595679145881</v>
       </c>
       <c r="E11">
-        <v>-7.191000000000001</v>
+        <v>-6.490000000000001</v>
       </c>
       <c r="F11">
-        <v>6.308999999999999</v>
+        <v>7.009999999999999</v>
       </c>
       <c r="G11">
         <v>3.6</v>
@@ -2311,28 +2311,28 @@
         <v>7.12</v>
       </c>
       <c r="M11">
-        <v>0.3173426999999999</v>
+        <v>0.3526029999999999</v>
       </c>
       <c r="N11">
-        <v>6.8026573</v>
+        <v>6.767397</v>
       </c>
       <c r="O11">
-        <v>0.68026573</v>
+        <v>0.6767397000000001</v>
       </c>
       <c r="P11">
-        <v>6.12239157</v>
+        <v>6.0906573</v>
       </c>
       <c r="Q11">
-        <v>6.842391569999999</v>
+        <v>6.8106573</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1156535821320006</v>
+        <v>0.1163584618709713</v>
       </c>
       <c r="T11">
-        <v>1.080612699480778</v>
+        <v>1.091516964864035</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2349,7 +2349,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.43631254161511</v>
+        <v>20.1926812874536</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2357,22 +2357,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1092496156838742</v>
+        <v>0.1091801716276278</v>
       </c>
       <c r="C12">
-        <v>65.0859567914588</v>
+        <v>64.44548075568275</v>
       </c>
       <c r="D12">
-        <v>68.49595679145881</v>
+        <v>68.55648075568276</v>
       </c>
       <c r="E12">
-        <v>-6.49</v>
+        <v>-5.789000000000001</v>
       </c>
       <c r="F12">
-        <v>7.01</v>
+        <v>7.710999999999999</v>
       </c>
       <c r="G12">
         <v>3.6</v>
@@ -2393,28 +2393,28 @@
         <v>7.12</v>
       </c>
       <c r="M12">
-        <v>0.3526029999999999</v>
+        <v>0.3878633</v>
       </c>
       <c r="N12">
-        <v>6.767397</v>
+        <v>6.7321367</v>
       </c>
       <c r="O12">
-        <v>0.6767397000000001</v>
+        <v>0.67321367</v>
       </c>
       <c r="P12">
-        <v>6.0906573</v>
+        <v>6.05892303</v>
       </c>
       <c r="Q12">
-        <v>6.8106573</v>
+        <v>6.77892303</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1163584618709713</v>
+        <v>0.1170791816040762</v>
       </c>
       <c r="T12">
-        <v>1.091516964864035</v>
+        <v>1.102666269918826</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.1926812874536</v>
+        <v>18.35698298859418</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2439,22 +2439,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1091801716276278</v>
+        <v>0.1091107275713815</v>
       </c>
       <c r="C13">
-        <v>64.44548075568275</v>
+        <v>63.80511177410636</v>
       </c>
       <c r="D13">
-        <v>68.55648075568276</v>
+        <v>68.61711177410636</v>
       </c>
       <c r="E13">
-        <v>-5.789000000000001</v>
+        <v>-5.088000000000001</v>
       </c>
       <c r="F13">
-        <v>7.710999999999999</v>
+        <v>8.411999999999999</v>
       </c>
       <c r="G13">
         <v>3.6</v>
@@ -2475,28 +2475,28 @@
         <v>7.12</v>
       </c>
       <c r="M13">
-        <v>0.3878633</v>
+        <v>0.4231235999999999</v>
       </c>
       <c r="N13">
-        <v>6.7321367</v>
+        <v>6.6968764</v>
       </c>
       <c r="O13">
-        <v>0.67321367</v>
+        <v>0.66968764</v>
       </c>
       <c r="P13">
-        <v>6.05892303</v>
+        <v>6.02718876</v>
       </c>
       <c r="Q13">
-        <v>6.77892303</v>
+        <v>6.747188759999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1170791816040762</v>
+        <v>0.1178162813311153</v>
       </c>
       <c r="T13">
-        <v>1.102666269918826</v>
+        <v>1.114068968270317</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.35698298859418</v>
+        <v>16.82723440621133</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2521,22 +2521,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1091107275713815</v>
+        <v>0.1090412835151352</v>
       </c>
       <c r="C14">
-        <v>63.80511177410636</v>
+        <v>63.16485013101571</v>
       </c>
       <c r="D14">
-        <v>68.61711177410636</v>
+        <v>68.67785013101572</v>
       </c>
       <c r="E14">
-        <v>-5.088000000000001</v>
+        <v>-4.387</v>
       </c>
       <c r="F14">
-        <v>8.411999999999999</v>
+        <v>9.113</v>
       </c>
       <c r="G14">
         <v>3.6</v>
@@ -2557,28 +2557,28 @@
         <v>7.12</v>
       </c>
       <c r="M14">
-        <v>0.4231235999999999</v>
+        <v>0.4583839</v>
       </c>
       <c r="N14">
-        <v>6.6968764</v>
+        <v>6.6616161</v>
       </c>
       <c r="O14">
-        <v>0.66968764</v>
+        <v>0.6661616100000001</v>
       </c>
       <c r="P14">
-        <v>6.02718876</v>
+        <v>5.99545449</v>
       </c>
       <c r="Q14">
-        <v>6.747188759999999</v>
+        <v>6.71545449</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1178162813311153</v>
+        <v>0.1185703258794657</v>
       </c>
       <c r="T14">
-        <v>1.114068968270317</v>
+        <v>1.125733797618393</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.82723440621133</v>
+        <v>15.53283175957969</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2603,22 +2603,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1090412835151352</v>
+        <v>0.1089718394588888</v>
       </c>
       <c r="C15">
-        <v>63.16485013101571</v>
+        <v>62.52469611170432</v>
       </c>
       <c r="D15">
-        <v>68.67785013101572</v>
+        <v>68.73869611170433</v>
       </c>
       <c r="E15">
-        <v>-4.387</v>
+        <v>-3.686</v>
       </c>
       <c r="F15">
-        <v>9.113</v>
+        <v>9.814</v>
       </c>
       <c r="G15">
         <v>3.6</v>
@@ -2639,28 +2639,28 @@
         <v>7.12</v>
       </c>
       <c r="M15">
-        <v>0.4583839</v>
+        <v>0.4936442</v>
       </c>
       <c r="N15">
-        <v>6.6616161</v>
+        <v>6.6263558</v>
       </c>
       <c r="O15">
-        <v>0.6661616100000001</v>
+        <v>0.66263558</v>
       </c>
       <c r="P15">
-        <v>5.99545449</v>
+        <v>5.96372022</v>
       </c>
       <c r="Q15">
-        <v>6.71545449</v>
+        <v>6.68372022</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1185703258794657</v>
+        <v>0.1193419063475451</v>
       </c>
       <c r="T15">
-        <v>1.125733797618393</v>
+        <v>1.137669902067588</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2677,7 +2677,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.53283175957969</v>
+        <v>14.42334377675257</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2685,22 +2685,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1089718394588888</v>
+        <v>0.1089023954026425</v>
       </c>
       <c r="C16">
-        <v>62.52469611170432</v>
+        <v>61.88465000247767</v>
       </c>
       <c r="D16">
-        <v>68.73869611170433</v>
+        <v>68.79965000247768</v>
       </c>
       <c r="E16">
-        <v>-3.686</v>
+        <v>-2.984999999999999</v>
       </c>
       <c r="F16">
-        <v>9.814</v>
+        <v>10.515</v>
       </c>
       <c r="G16">
         <v>3.6</v>
@@ -2721,28 +2721,28 @@
         <v>7.12</v>
       </c>
       <c r="M16">
-        <v>0.4936442</v>
+        <v>0.5289045</v>
       </c>
       <c r="N16">
-        <v>6.6263558</v>
+        <v>6.5910955</v>
       </c>
       <c r="O16">
-        <v>0.66263558</v>
+        <v>0.65910955</v>
       </c>
       <c r="P16">
-        <v>5.96372022</v>
+        <v>5.93198595</v>
       </c>
       <c r="Q16">
-        <v>6.68372022</v>
+        <v>6.651985949999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1193419063475451</v>
+        <v>0.1201316416501676</v>
       </c>
       <c r="T16">
-        <v>1.137669902067588</v>
+        <v>1.149886856033235</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.42334377675257</v>
+        <v>13.46178752496906</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2767,22 +2767,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1089023954026425</v>
+        <v>0.1090489513463961</v>
       </c>
       <c r="C17">
-        <v>61.88465000247767</v>
+        <v>61.05513827983213</v>
       </c>
       <c r="D17">
-        <v>68.79965000247768</v>
+        <v>68.67113827983214</v>
       </c>
       <c r="E17">
-        <v>-2.985000000000001</v>
+        <v>-2.284000000000001</v>
       </c>
       <c r="F17">
-        <v>10.515</v>
+        <v>11.216</v>
       </c>
       <c r="G17">
         <v>3.6</v>
@@ -2803,45 +2803,45 @@
         <v>7.12</v>
       </c>
       <c r="M17">
-        <v>0.5289044999999999</v>
+        <v>0.5809888</v>
       </c>
       <c r="N17">
-        <v>6.5910955</v>
+        <v>6.5390112</v>
       </c>
       <c r="O17">
-        <v>0.65910955</v>
+        <v>0.65390112</v>
       </c>
       <c r="P17">
-        <v>5.93198595</v>
+        <v>5.88511008</v>
       </c>
       <c r="Q17">
-        <v>6.651985949999999</v>
+        <v>6.60511008</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1201316416501676</v>
+        <v>0.1209401801742811</v>
       </c>
       <c r="T17">
-        <v>1.149886856033235</v>
+        <v>1.162394689855206</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.1</v>
       </c>
       <c r="W17">
-        <v>0.04527</v>
+        <v>0.04662</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.46178752496906</v>
+        <v>12.25496945896375</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2849,22 +2849,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1090489513463961</v>
+        <v>0.1089930072901498</v>
       </c>
       <c r="C18">
-        <v>61.05513827983213</v>
+        <v>60.40313771263011</v>
       </c>
       <c r="D18">
-        <v>68.67113827983214</v>
+        <v>68.72013771263012</v>
       </c>
       <c r="E18">
-        <v>-2.284000000000001</v>
+        <v>-1.583</v>
       </c>
       <c r="F18">
-        <v>11.216</v>
+        <v>11.917</v>
       </c>
       <c r="G18">
         <v>3.6</v>
@@ -2885,28 +2885,28 @@
         <v>7.12</v>
       </c>
       <c r="M18">
-        <v>0.5809888</v>
+        <v>0.6173006</v>
       </c>
       <c r="N18">
-        <v>6.5390112</v>
+        <v>6.5026994</v>
       </c>
       <c r="O18">
-        <v>0.65390112</v>
+        <v>0.65026994</v>
       </c>
       <c r="P18">
-        <v>5.88511008</v>
+        <v>5.85242946</v>
       </c>
       <c r="Q18">
-        <v>6.60511008</v>
+        <v>6.57242946</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1209401801742811</v>
+        <v>0.1217682015543974</v>
       </c>
       <c r="T18">
-        <v>1.162394689855206</v>
+        <v>1.175203917263249</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.25496945896375</v>
+        <v>11.53408890255412</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2931,22 +2931,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1089930072901498</v>
+        <v>0.1089370632339035</v>
       </c>
       <c r="C19">
-        <v>60.40313771263011</v>
+        <v>59.75120712122465</v>
       </c>
       <c r="D19">
-        <v>68.72013771263012</v>
+        <v>68.76920712122465</v>
       </c>
       <c r="E19">
-        <v>-1.583</v>
+        <v>-0.8819999999999997</v>
       </c>
       <c r="F19">
-        <v>11.917</v>
+        <v>12.618</v>
       </c>
       <c r="G19">
         <v>3.6</v>
@@ -2967,28 +2967,28 @@
         <v>7.12</v>
       </c>
       <c r="M19">
-        <v>0.6173006</v>
+        <v>0.6536124</v>
       </c>
       <c r="N19">
-        <v>6.5026994</v>
+        <v>6.4663876</v>
       </c>
       <c r="O19">
-        <v>0.65026994</v>
+        <v>0.6466387600000001</v>
       </c>
       <c r="P19">
-        <v>5.85242946</v>
+        <v>5.81974884</v>
       </c>
       <c r="Q19">
-        <v>6.57242946</v>
+        <v>6.53974884</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1217682015543974</v>
+        <v>0.1226164185779311</v>
       </c>
       <c r="T19">
-        <v>1.175203917263249</v>
+        <v>1.188325564851976</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.53408890255412</v>
+        <v>10.89330618574556</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3013,22 +3013,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1089370632339035</v>
+        <v>0.1088811191776571</v>
       </c>
       <c r="C20">
-        <v>59.75120712122464</v>
+        <v>59.09934665562091</v>
       </c>
       <c r="D20">
-        <v>68.76920712122464</v>
+        <v>68.81834665562091</v>
       </c>
       <c r="E20">
-        <v>-0.8820000000000014</v>
+        <v>-0.1810000000000009</v>
       </c>
       <c r="F20">
-        <v>12.618</v>
+        <v>13.319</v>
       </c>
       <c r="G20">
         <v>3.6</v>
@@ -3049,28 +3049,28 @@
         <v>7.12</v>
       </c>
       <c r="M20">
-        <v>0.6536123999999999</v>
+        <v>0.6899242</v>
       </c>
       <c r="N20">
-        <v>6.4663876</v>
+        <v>6.4300758</v>
       </c>
       <c r="O20">
-        <v>0.6466387600000001</v>
+        <v>0.64300758</v>
       </c>
       <c r="P20">
-        <v>5.81974884</v>
+        <v>5.78706822</v>
       </c>
       <c r="Q20">
-        <v>6.53974884</v>
+        <v>6.50706822</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1226164185779311</v>
+        <v>0.1234855792316755</v>
       </c>
       <c r="T20">
-        <v>1.188325564851976</v>
+        <v>1.20177120373919</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.89330618574556</v>
+        <v>10.31997428123263</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1088811191776571</v>
+        <v>0.1091311751214108</v>
       </c>
       <c r="C21">
-        <v>59.09934665562091</v>
+        <v>58.17924805413968</v>
       </c>
       <c r="D21">
-        <v>68.81834665562091</v>
+        <v>68.59924805413968</v>
       </c>
       <c r="E21">
-        <v>-0.1810000000000009</v>
+        <v>0.5199999999999996</v>
       </c>
       <c r="F21">
-        <v>13.319</v>
+        <v>14.02</v>
       </c>
       <c r="G21">
         <v>3.6</v>
@@ -3131,45 +3131,45 @@
         <v>7.12</v>
       </c>
       <c r="M21">
-        <v>0.6899242</v>
+        <v>0.75007</v>
       </c>
       <c r="N21">
-        <v>6.4300758</v>
+        <v>6.36993</v>
       </c>
       <c r="O21">
-        <v>0.64300758</v>
+        <v>0.636993</v>
       </c>
       <c r="P21">
-        <v>5.78706822</v>
+        <v>5.732937</v>
       </c>
       <c r="Q21">
-        <v>6.50706822</v>
+        <v>6.452936999999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1234855792316755</v>
+        <v>0.1243764689017635</v>
       </c>
       <c r="T21">
-        <v>1.20177120373919</v>
+        <v>1.215552983598585</v>
       </c>
       <c r="U21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0.1</v>
       </c>
       <c r="W21">
-        <v>0.04662</v>
+        <v>0.04815</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>10.31997428123263</v>
+        <v>9.492447371578653</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3177,22 +3177,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1091311751214108</v>
+        <v>0.1090905310651644</v>
       </c>
       <c r="C22">
-        <v>58.17924805413968</v>
+        <v>57.51376530849606</v>
       </c>
       <c r="D22">
-        <v>68.59924805413968</v>
+        <v>68.63476530849607</v>
       </c>
       <c r="E22">
-        <v>0.5199999999999996</v>
+        <v>1.221</v>
       </c>
       <c r="F22">
-        <v>14.02</v>
+        <v>14.721</v>
       </c>
       <c r="G22">
         <v>3.6</v>
@@ -3213,28 +3213,28 @@
         <v>7.12</v>
       </c>
       <c r="M22">
-        <v>0.75007</v>
+        <v>0.7875735</v>
       </c>
       <c r="N22">
-        <v>6.36993</v>
+        <v>6.3324265</v>
       </c>
       <c r="O22">
-        <v>0.636993</v>
+        <v>0.6332426500000001</v>
       </c>
       <c r="P22">
-        <v>5.732937</v>
+        <v>5.699183850000001</v>
       </c>
       <c r="Q22">
-        <v>6.452936999999999</v>
+        <v>6.41918385</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1243764689017635</v>
+        <v>0.1252899127407145</v>
       </c>
       <c r="T22">
-        <v>1.215552983598585</v>
+        <v>1.229683669277204</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.492447371578653</v>
+        <v>9.040426068170145</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3259,22 +3259,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1090905310651644</v>
+        <v>0.1090498870089181</v>
       </c>
       <c r="C23">
-        <v>57.51376530849607</v>
+        <v>56.84831936001447</v>
       </c>
       <c r="D23">
-        <v>68.63476530849607</v>
+        <v>68.67031936001447</v>
       </c>
       <c r="E23">
-        <v>1.220999999999998</v>
+        <v>1.921999999999999</v>
       </c>
       <c r="F23">
-        <v>14.721</v>
+        <v>15.422</v>
       </c>
       <c r="G23">
         <v>3.6</v>
@@ -3295,28 +3295,28 @@
         <v>7.12</v>
       </c>
       <c r="M23">
-        <v>0.7875734999999999</v>
+        <v>0.8250769999999999</v>
       </c>
       <c r="N23">
-        <v>6.3324265</v>
+        <v>6.294923</v>
       </c>
       <c r="O23">
-        <v>0.6332426500000001</v>
+        <v>0.6294923</v>
       </c>
       <c r="P23">
-        <v>5.699183850000001</v>
+        <v>5.6654307</v>
       </c>
       <c r="Q23">
-        <v>6.41918385</v>
+        <v>6.3854307</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1252899127407145</v>
+        <v>0.1262267782165617</v>
       </c>
       <c r="T23">
-        <v>1.229683669277204</v>
+        <v>1.244176680229634</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.040426068170147</v>
+        <v>8.629497610526048</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3341,22 +3341,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1090498870089181</v>
+        <v>0.1090092429526718</v>
       </c>
       <c r="C24">
-        <v>56.84831936001447</v>
+        <v>56.18291026590936</v>
       </c>
       <c r="D24">
-        <v>68.67031936001447</v>
+        <v>68.70591026590937</v>
       </c>
       <c r="E24">
-        <v>1.921999999999999</v>
+        <v>2.623000000000001</v>
       </c>
       <c r="F24">
-        <v>15.422</v>
+        <v>16.123</v>
       </c>
       <c r="G24">
         <v>3.6</v>
@@ -3377,28 +3377,28 @@
         <v>7.12</v>
       </c>
       <c r="M24">
-        <v>0.8250769999999999</v>
+        <v>0.8625805000000001</v>
       </c>
       <c r="N24">
-        <v>6.294923</v>
+        <v>6.2574195</v>
       </c>
       <c r="O24">
-        <v>0.6294923</v>
+        <v>0.6257419500000001</v>
       </c>
       <c r="P24">
-        <v>5.6654307</v>
+        <v>5.63167755</v>
       </c>
       <c r="Q24">
-        <v>6.3854307</v>
+        <v>6.35167755</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1262267782165617</v>
+        <v>0.1271879778606127</v>
       </c>
       <c r="T24">
-        <v>1.244176680229634</v>
+        <v>1.259046133024985</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.629497610526048</v>
+        <v>8.254302062242306</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3423,22 +3423,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1090092429526718</v>
+        <v>0.1089685988964254</v>
       </c>
       <c r="C25">
-        <v>56.18291026590936</v>
+        <v>55.51753808351387</v>
       </c>
       <c r="D25">
-        <v>68.70591026590937</v>
+        <v>68.74153808351387</v>
       </c>
       <c r="E25">
-        <v>2.623000000000001</v>
+        <v>3.324000000000002</v>
       </c>
       <c r="F25">
-        <v>16.123</v>
+        <v>16.824</v>
       </c>
       <c r="G25">
         <v>3.6</v>
@@ -3459,28 +3459,28 @@
         <v>7.12</v>
       </c>
       <c r="M25">
-        <v>0.8625805000000001</v>
+        <v>0.9000840000000001</v>
       </c>
       <c r="N25">
-        <v>6.2574195</v>
+        <v>6.219916</v>
       </c>
       <c r="O25">
-        <v>0.6257419500000001</v>
+        <v>0.6219916</v>
       </c>
       <c r="P25">
-        <v>5.63167755</v>
+        <v>5.597924399999999</v>
       </c>
       <c r="Q25">
-        <v>6.35167755</v>
+        <v>6.317924399999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1271879778606127</v>
+        <v>0.1281744722321387</v>
       </c>
       <c r="T25">
-        <v>1.259046133024985</v>
+        <v>1.274306887209687</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.254302062242306</v>
+        <v>7.910372809648876</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3505,22 +3505,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1089685988964254</v>
+        <v>0.1091079548401791</v>
       </c>
       <c r="C26">
-        <v>55.51753808351387</v>
+        <v>54.69453484882762</v>
       </c>
       <c r="D26">
-        <v>68.74153808351387</v>
+        <v>68.61953484882763</v>
       </c>
       <c r="E26">
-        <v>3.323999999999998</v>
+        <v>4.024999999999999</v>
       </c>
       <c r="F26">
-        <v>16.824</v>
+        <v>17.525</v>
       </c>
       <c r="G26">
         <v>3.6</v>
@@ -3541,45 +3541,45 @@
         <v>7.12</v>
       </c>
       <c r="M26">
-        <v>0.9000839999999999</v>
+        <v>0.9516074999999999</v>
       </c>
       <c r="N26">
-        <v>6.219916</v>
+        <v>6.1683925</v>
       </c>
       <c r="O26">
-        <v>0.6219916000000001</v>
+        <v>0.6168392500000001</v>
       </c>
       <c r="P26">
-        <v>5.5979244</v>
+        <v>5.55155325</v>
       </c>
       <c r="Q26">
-        <v>6.3179244</v>
+        <v>6.27155325</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1281744722321387</v>
+        <v>0.1291872731202388</v>
       </c>
       <c r="T26">
-        <v>1.274306887209687</v>
+        <v>1.289974594839314</v>
       </c>
       <c r="U26">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V26">
         <v>0.1</v>
       </c>
       <c r="W26">
-        <v>0.04815</v>
+        <v>0.04887</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>7.910372809648878</v>
+        <v>7.482076381281149</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3587,22 +3587,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1091079548401791</v>
+        <v>0.1090745107839328</v>
       </c>
       <c r="C27">
-        <v>54.69453484882762</v>
+        <v>54.02277491424046</v>
       </c>
       <c r="D27">
-        <v>68.61953484882763</v>
+        <v>68.64877491424046</v>
       </c>
       <c r="E27">
-        <v>4.024999999999999</v>
+        <v>4.725999999999999</v>
       </c>
       <c r="F27">
-        <v>17.525</v>
+        <v>18.226</v>
       </c>
       <c r="G27">
         <v>3.6</v>
@@ -3623,28 +3623,28 @@
         <v>7.12</v>
       </c>
       <c r="M27">
-        <v>0.9516074999999999</v>
+        <v>0.9896718</v>
       </c>
       <c r="N27">
-        <v>6.1683925</v>
+        <v>6.1303282</v>
       </c>
       <c r="O27">
-        <v>0.6168392500000001</v>
+        <v>0.61303282</v>
       </c>
       <c r="P27">
-        <v>5.55155325</v>
+        <v>5.51729538</v>
       </c>
       <c r="Q27">
-        <v>6.27155325</v>
+        <v>6.23729538</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1291872731202388</v>
+        <v>0.1302274470053146</v>
       </c>
       <c r="T27">
-        <v>1.289974594839314</v>
+        <v>1.306065754026499</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.482076381281149</v>
+        <v>7.194304212770334</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3669,22 +3669,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1090745107839328</v>
+        <v>0.1090410667276864</v>
       </c>
       <c r="C28">
-        <v>54.02277491424046</v>
+        <v>53.35103990975244</v>
       </c>
       <c r="D28">
-        <v>68.64877491424046</v>
+        <v>68.67803990975244</v>
       </c>
       <c r="E28">
-        <v>4.725999999999999</v>
+        <v>5.427</v>
       </c>
       <c r="F28">
-        <v>18.226</v>
+        <v>18.927</v>
       </c>
       <c r="G28">
         <v>3.6</v>
@@ -3705,28 +3705,28 @@
         <v>7.12</v>
       </c>
       <c r="M28">
-        <v>0.9896718</v>
+        <v>1.0277361</v>
       </c>
       <c r="N28">
-        <v>6.1303282</v>
+        <v>6.0922639</v>
       </c>
       <c r="O28">
-        <v>0.61303282</v>
+        <v>0.60922639</v>
       </c>
       <c r="P28">
-        <v>5.51729538</v>
+        <v>5.48303751</v>
       </c>
       <c r="Q28">
-        <v>6.23729538</v>
+        <v>6.20303751</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1302274470053146</v>
+        <v>0.1312961188050499</v>
       </c>
       <c r="T28">
-        <v>1.306065754026499</v>
+        <v>1.322597766890045</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.194304212770334</v>
+        <v>6.927848501186248</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3751,22 +3751,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1090410667276864</v>
+        <v>0.1090076226714401</v>
       </c>
       <c r="C29">
-        <v>53.35103990975244</v>
+        <v>52.67932986726032</v>
       </c>
       <c r="D29">
-        <v>68.67803990975244</v>
+        <v>68.70732986726033</v>
       </c>
       <c r="E29">
-        <v>5.427</v>
+        <v>6.128</v>
       </c>
       <c r="F29">
-        <v>18.927</v>
+        <v>19.628</v>
       </c>
       <c r="G29">
         <v>3.6</v>
@@ -3787,28 +3787,28 @@
         <v>7.12</v>
       </c>
       <c r="M29">
-        <v>1.0277361</v>
+        <v>1.0658004</v>
       </c>
       <c r="N29">
-        <v>6.0922639</v>
+        <v>6.0541996</v>
       </c>
       <c r="O29">
-        <v>0.60922639</v>
+        <v>0.6054199600000001</v>
       </c>
       <c r="P29">
-        <v>5.48303751</v>
+        <v>5.448779640000001</v>
       </c>
       <c r="Q29">
-        <v>6.20303751</v>
+        <v>6.16877964</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1312961188050499</v>
+        <v>0.1323944759325557</v>
       </c>
       <c r="T29">
-        <v>1.322597766890045</v>
+        <v>1.339589002333134</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.927848501186248</v>
+        <v>6.680425340429596</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3833,22 +3833,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1090076226714401</v>
+        <v>0.1089741786151937</v>
       </c>
       <c r="C30">
-        <v>52.67932986726032</v>
+        <v>52.00764481871527</v>
       </c>
       <c r="D30">
-        <v>68.70732986726033</v>
+        <v>68.73664481871528</v>
       </c>
       <c r="E30">
-        <v>6.128</v>
+        <v>6.829000000000001</v>
       </c>
       <c r="F30">
-        <v>19.628</v>
+        <v>20.329</v>
       </c>
       <c r="G30">
         <v>3.6</v>
@@ -3869,28 +3869,28 @@
         <v>7.12</v>
       </c>
       <c r="M30">
-        <v>1.0658004</v>
+        <v>1.1038647</v>
       </c>
       <c r="N30">
-        <v>6.0541996</v>
+        <v>6.0161353</v>
       </c>
       <c r="O30">
-        <v>0.6054199600000001</v>
+        <v>0.6016135300000001</v>
       </c>
       <c r="P30">
-        <v>5.448779640000001</v>
+        <v>5.41452177</v>
       </c>
       <c r="Q30">
-        <v>6.16877964</v>
+        <v>6.13452177</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1323944759325557</v>
+        <v>0.133523772697456</v>
       </c>
       <c r="T30">
-        <v>1.339589002333134</v>
+        <v>1.357058864126733</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.680425340429596</v>
+        <v>6.450065845932023</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3915,22 +3915,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1089741786151937</v>
+        <v>0.1089407345589474</v>
       </c>
       <c r="C31">
-        <v>52.00764481871528</v>
+        <v>51.33598479612294</v>
       </c>
       <c r="D31">
-        <v>68.73664481871528</v>
+        <v>68.76598479612295</v>
       </c>
       <c r="E31">
-        <v>6.828999999999997</v>
+        <v>7.529999999999998</v>
       </c>
       <c r="F31">
-        <v>20.329</v>
+        <v>21.03</v>
       </c>
       <c r="G31">
         <v>3.6</v>
@@ -3951,28 +3951,28 @@
         <v>7.12</v>
       </c>
       <c r="M31">
-        <v>1.1038647</v>
+        <v>1.141929</v>
       </c>
       <c r="N31">
-        <v>6.0161353</v>
+        <v>5.978071</v>
       </c>
       <c r="O31">
-        <v>0.6016135300000001</v>
+        <v>0.5978071</v>
       </c>
       <c r="P31">
-        <v>5.41452177</v>
+        <v>5.3802639</v>
       </c>
       <c r="Q31">
-        <v>6.13452177</v>
+        <v>6.1002639</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.133523772697456</v>
+        <v>0.1346853350842106</v>
       </c>
       <c r="T31">
-        <v>1.357058864126732</v>
+        <v>1.37502786482872</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.450065845932024</v>
+        <v>6.235063651067623</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3997,22 +3997,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1089407345589474</v>
+        <v>0.1091862905027011</v>
       </c>
       <c r="C32">
-        <v>51.33598479612294</v>
+        <v>50.42014355368848</v>
       </c>
       <c r="D32">
-        <v>68.76598479612295</v>
+        <v>68.55114355368848</v>
       </c>
       <c r="E32">
-        <v>7.529999999999998</v>
+        <v>8.230999999999998</v>
       </c>
       <c r="F32">
-        <v>21.03</v>
+        <v>21.731</v>
       </c>
       <c r="G32">
         <v>3.6</v>
@@ -4033,45 +4033,45 @@
         <v>7.12</v>
       </c>
       <c r="M32">
-        <v>1.141929</v>
+        <v>1.2017243</v>
       </c>
       <c r="N32">
-        <v>5.978071</v>
+        <v>5.918275700000001</v>
       </c>
       <c r="O32">
-        <v>0.5978071</v>
+        <v>0.5918275700000001</v>
       </c>
       <c r="P32">
-        <v>5.3802639</v>
+        <v>5.32644813</v>
       </c>
       <c r="Q32">
-        <v>6.1002639</v>
+        <v>6.04644813</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1346853350842106</v>
+        <v>0.1358805659459436</v>
       </c>
       <c r="T32">
-        <v>1.37502786482872</v>
+        <v>1.393517706130764</v>
       </c>
       <c r="U32">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V32">
         <v>0.1</v>
       </c>
       <c r="W32">
-        <v>0.04887</v>
+        <v>0.04977</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>6.235063651067623</v>
+        <v>5.924819860928168</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4079,22 +4079,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1091862905027011</v>
+        <v>0.1091618464464547</v>
       </c>
       <c r="C33">
-        <v>50.42014355368848</v>
+        <v>49.74046990722768</v>
       </c>
       <c r="D33">
-        <v>68.55114355368848</v>
+        <v>68.57246990722768</v>
       </c>
       <c r="E33">
-        <v>8.230999999999998</v>
+        <v>8.931999999999999</v>
       </c>
       <c r="F33">
-        <v>21.731</v>
+        <v>22.432</v>
       </c>
       <c r="G33">
         <v>3.6</v>
@@ -4115,28 +4115,28 @@
         <v>7.12</v>
       </c>
       <c r="M33">
-        <v>1.2017243</v>
+        <v>1.2404896</v>
       </c>
       <c r="N33">
-        <v>5.918275700000001</v>
+        <v>5.8795104</v>
       </c>
       <c r="O33">
-        <v>0.5918275700000001</v>
+        <v>0.58795104</v>
       </c>
       <c r="P33">
-        <v>5.32644813</v>
+        <v>5.29155936</v>
       </c>
       <c r="Q33">
-        <v>6.04644813</v>
+        <v>6.01155936</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1358805659459436</v>
+        <v>0.1371109506565511</v>
       </c>
       <c r="T33">
-        <v>1.393517706130764</v>
+        <v>1.412551366294634</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.924819860928168</v>
+        <v>5.739669240274163</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1091618464464547</v>
+        <v>0.1091374023902084</v>
       </c>
       <c r="C34">
-        <v>49.74046990722768</v>
+        <v>49.06080953421119</v>
       </c>
       <c r="D34">
-        <v>68.57246990722768</v>
+        <v>68.59380953421119</v>
       </c>
       <c r="E34">
-        <v>8.931999999999999</v>
+        <v>9.632999999999999</v>
       </c>
       <c r="F34">
-        <v>22.432</v>
+        <v>23.133</v>
       </c>
       <c r="G34">
         <v>3.6</v>
@@ -4197,28 +4197,28 @@
         <v>7.12</v>
       </c>
       <c r="M34">
-        <v>1.2404896</v>
+        <v>1.2792549</v>
       </c>
       <c r="N34">
-        <v>5.8795104</v>
+        <v>5.8407451</v>
       </c>
       <c r="O34">
-        <v>0.58795104</v>
+        <v>0.5840745100000001</v>
       </c>
       <c r="P34">
-        <v>5.29155936</v>
+        <v>5.256670590000001</v>
       </c>
       <c r="Q34">
-        <v>6.01155936</v>
+        <v>5.97667059</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1371109506565511</v>
+        <v>0.1383780632689678</v>
       </c>
       <c r="T34">
-        <v>1.412551366294634</v>
+        <v>1.432153195418619</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.739669240274163</v>
+        <v>5.565739869356764</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4243,22 +4243,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1091374023902084</v>
+        <v>0.1091129583339621</v>
       </c>
       <c r="C35">
-        <v>49.06080953421119</v>
+        <v>48.38116244703484</v>
       </c>
       <c r="D35">
-        <v>68.59380953421119</v>
+        <v>68.61516244703485</v>
       </c>
       <c r="E35">
-        <v>9.632999999999999</v>
+        <v>10.334</v>
       </c>
       <c r="F35">
-        <v>23.133</v>
+        <v>23.834</v>
       </c>
       <c r="G35">
         <v>3.6</v>
@@ -4279,28 +4279,28 @@
         <v>7.12</v>
       </c>
       <c r="M35">
-        <v>1.2792549</v>
+        <v>1.3180202</v>
       </c>
       <c r="N35">
-        <v>5.8407451</v>
+        <v>5.8019798</v>
       </c>
       <c r="O35">
-        <v>0.5840745100000001</v>
+        <v>0.58019798</v>
       </c>
       <c r="P35">
-        <v>5.256670590000001</v>
+        <v>5.221781819999999</v>
       </c>
       <c r="Q35">
-        <v>5.97667059</v>
+        <v>5.941781819999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1383780632689678</v>
+        <v>0.1396835732332759</v>
       </c>
       <c r="T35">
-        <v>1.432153195418619</v>
+        <v>1.452349019364543</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.565739869356764</v>
+        <v>5.402041637905094</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4325,22 +4325,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1091129583339621</v>
+        <v>0.1090885142777157</v>
       </c>
       <c r="C36">
-        <v>48.38116244703484</v>
+        <v>47.70152865810999</v>
       </c>
       <c r="D36">
-        <v>68.61516244703485</v>
+        <v>68.63652865811</v>
       </c>
       <c r="E36">
-        <v>10.334</v>
+        <v>11.035</v>
       </c>
       <c r="F36">
-        <v>23.834</v>
+        <v>24.535</v>
       </c>
       <c r="G36">
         <v>3.6</v>
@@ -4361,28 +4361,28 @@
         <v>7.12</v>
       </c>
       <c r="M36">
-        <v>1.3180202</v>
+        <v>1.3567855</v>
       </c>
       <c r="N36">
-        <v>5.8019798</v>
+        <v>5.7632145</v>
       </c>
       <c r="O36">
-        <v>0.58019798</v>
+        <v>0.57632145</v>
       </c>
       <c r="P36">
-        <v>5.221781819999999</v>
+        <v>5.18689305</v>
       </c>
       <c r="Q36">
-        <v>5.941781819999999</v>
+        <v>5.90689305</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1396835732332759</v>
+        <v>0.1410292527349473</v>
       </c>
       <c r="T36">
-        <v>1.452349019364543</v>
+        <v>1.473166253278033</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.402041637905094</v>
+        <v>5.247697591107806</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4407,22 +4407,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1090885142777157</v>
+        <v>0.1090640702214694</v>
       </c>
       <c r="C37">
-        <v>47.70152865810999</v>
+        <v>47.02190817986333</v>
       </c>
       <c r="D37">
-        <v>68.63652865811</v>
+        <v>68.65790817986334</v>
       </c>
       <c r="E37">
-        <v>11.035</v>
+        <v>11.736</v>
       </c>
       <c r="F37">
-        <v>24.535</v>
+        <v>25.236</v>
       </c>
       <c r="G37">
         <v>3.6</v>
@@ -4443,28 +4443,28 @@
         <v>7.12</v>
       </c>
       <c r="M37">
-        <v>1.3567855</v>
+        <v>1.3955508</v>
       </c>
       <c r="N37">
-        <v>5.7632145</v>
+        <v>5.7244492</v>
       </c>
       <c r="O37">
-        <v>0.57632145</v>
+        <v>0.57244492</v>
       </c>
       <c r="P37">
-        <v>5.18689305</v>
+        <v>5.152004280000001</v>
       </c>
       <c r="Q37">
-        <v>5.90689305</v>
+        <v>5.872004280000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1410292527349473</v>
+        <v>0.1424169847210459</v>
       </c>
       <c r="T37">
-        <v>1.473166253278033</v>
+        <v>1.494634025751321</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.247697591107806</v>
+        <v>5.101928213577033</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4489,22 +4489,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1090640702214694</v>
+        <v>0.109039626165223</v>
       </c>
       <c r="C38">
-        <v>47.02190817986331</v>
+        <v>46.34230102473722</v>
       </c>
       <c r="D38">
-        <v>68.65790817986331</v>
+        <v>68.67930102473723</v>
       </c>
       <c r="E38">
-        <v>11.736</v>
+        <v>12.437</v>
       </c>
       <c r="F38">
-        <v>25.236</v>
+        <v>25.937</v>
       </c>
       <c r="G38">
         <v>3.6</v>
@@ -4525,28 +4525,28 @@
         <v>7.12</v>
       </c>
       <c r="M38">
-        <v>1.3955508</v>
+        <v>1.4343161</v>
       </c>
       <c r="N38">
-        <v>5.7244492</v>
+        <v>5.6856839</v>
       </c>
       <c r="O38">
-        <v>0.57244492</v>
+        <v>0.56856839</v>
       </c>
       <c r="P38">
-        <v>5.152004280000001</v>
+        <v>5.11711551</v>
       </c>
       <c r="Q38">
-        <v>5.872004280000001</v>
+        <v>5.837115509999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1424169847210459</v>
+        <v>0.1438487716908302</v>
       </c>
       <c r="T38">
-        <v>1.494634025751321</v>
+        <v>1.516783314811062</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.101928213577034</v>
+        <v>4.964038261858735</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4571,22 +4571,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.109039626165223</v>
+        <v>0.1090151821089767</v>
       </c>
       <c r="C39">
-        <v>46.34230102473722</v>
+        <v>45.66270720518938</v>
       </c>
       <c r="D39">
-        <v>68.67930102473723</v>
+        <v>68.70070720518939</v>
       </c>
       <c r="E39">
-        <v>12.437</v>
+        <v>13.138</v>
       </c>
       <c r="F39">
-        <v>25.937</v>
+        <v>26.638</v>
       </c>
       <c r="G39">
         <v>3.6</v>
@@ -4607,28 +4607,28 @@
         <v>7.12</v>
       </c>
       <c r="M39">
-        <v>1.4343161</v>
+        <v>1.4730814</v>
       </c>
       <c r="N39">
-        <v>5.6856839</v>
+        <v>5.6469186</v>
       </c>
       <c r="O39">
-        <v>0.56856839</v>
+        <v>0.56469186</v>
       </c>
       <c r="P39">
-        <v>5.11711551</v>
+        <v>5.08222674</v>
       </c>
       <c r="Q39">
-        <v>5.837115509999999</v>
+        <v>5.80222674</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1438487716908302</v>
+        <v>0.1453267453370592</v>
       </c>
       <c r="T39">
-        <v>1.516783314811062</v>
+        <v>1.539647097066278</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.964038261858735</v>
+        <v>4.833405676020348</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4653,22 +4653,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1090151821089767</v>
+        <v>0.1089907380527304</v>
       </c>
       <c r="C40">
-        <v>45.66270720518938</v>
+        <v>44.98312673369315</v>
       </c>
       <c r="D40">
-        <v>68.70070720518939</v>
+        <v>68.72212673369316</v>
       </c>
       <c r="E40">
-        <v>13.138</v>
+        <v>13.839</v>
       </c>
       <c r="F40">
-        <v>26.638</v>
+        <v>27.339</v>
       </c>
       <c r="G40">
         <v>3.6</v>
@@ -4689,28 +4689,28 @@
         <v>7.12</v>
       </c>
       <c r="M40">
-        <v>1.4730814</v>
+        <v>1.5118467</v>
       </c>
       <c r="N40">
-        <v>5.6469186</v>
+        <v>5.6081533</v>
       </c>
       <c r="O40">
-        <v>0.56469186</v>
+        <v>0.5608153299999999</v>
       </c>
       <c r="P40">
-        <v>5.08222674</v>
+        <v>5.04733797</v>
       </c>
       <c r="Q40">
-        <v>5.80222674</v>
+        <v>5.76733797</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1453267453370592</v>
+        <v>0.1468531771356236</v>
       </c>
       <c r="T40">
-        <v>1.539647097066278</v>
+        <v>1.563260511526584</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.833405676020348</v>
+        <v>4.709472197148031</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4735,22 +4735,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1089907380527304</v>
+        <v>0.1089662939964841</v>
       </c>
       <c r="C41">
-        <v>44.98312673369315</v>
+        <v>44.30355962273739</v>
       </c>
       <c r="D41">
-        <v>68.72212673369316</v>
+        <v>68.74355962273739</v>
       </c>
       <c r="E41">
-        <v>13.839</v>
+        <v>14.54</v>
       </c>
       <c r="F41">
-        <v>27.339</v>
+        <v>28.04</v>
       </c>
       <c r="G41">
         <v>3.6</v>
@@ -4771,28 +4771,28 @@
         <v>7.12</v>
       </c>
       <c r="M41">
-        <v>1.5118467</v>
+        <v>1.550612</v>
       </c>
       <c r="N41">
-        <v>5.6081533</v>
+        <v>5.569388</v>
       </c>
       <c r="O41">
-        <v>0.5608153299999999</v>
+        <v>0.5569388000000001</v>
       </c>
       <c r="P41">
-        <v>5.04733797</v>
+        <v>5.0124492</v>
       </c>
       <c r="Q41">
-        <v>5.76733797</v>
+        <v>5.7324492</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1468531771356236</v>
+        <v>0.1484304899941401</v>
       </c>
       <c r="T41">
-        <v>1.563260511526584</v>
+        <v>1.587661039802233</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4809,7 +4809,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.709472197148031</v>
+        <v>4.59173539221933</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4817,22 +4817,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1089662939964841</v>
+        <v>0.1098643499402377</v>
       </c>
       <c r="C42">
-        <v>44.30355962273739</v>
+        <v>42.8238091141916</v>
       </c>
       <c r="D42">
-        <v>68.74355962273739</v>
+        <v>67.96480911419161</v>
       </c>
       <c r="E42">
-        <v>14.54</v>
+        <v>15.241</v>
       </c>
       <c r="F42">
-        <v>28.04</v>
+        <v>28.741</v>
       </c>
       <c r="G42">
         <v>3.6</v>
@@ -4853,45 +4853,45 @@
         <v>7.12</v>
       </c>
       <c r="M42">
-        <v>1.550612</v>
+        <v>1.6612298</v>
       </c>
       <c r="N42">
-        <v>5.569388</v>
+        <v>5.4587702</v>
       </c>
       <c r="O42">
-        <v>0.5569388000000001</v>
+        <v>0.54587702</v>
       </c>
       <c r="P42">
-        <v>5.0124492</v>
+        <v>4.91289318</v>
       </c>
       <c r="Q42">
-        <v>5.7324492</v>
+        <v>5.63289318</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1484304899941401</v>
+        <v>0.1500612710851487</v>
       </c>
       <c r="T42">
-        <v>1.587661039802233</v>
+        <v>1.612888704629599</v>
       </c>
       <c r="U42">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V42">
         <v>0.1</v>
       </c>
       <c r="W42">
-        <v>0.04977</v>
+        <v>0.05202</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.59173539221933</v>
+        <v>4.285981385597585</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4899,22 +4899,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1098643499402377</v>
+        <v>0.1098624058839914</v>
       </c>
       <c r="C43">
-        <v>42.8238091141916</v>
+        <v>42.12447584902835</v>
       </c>
       <c r="D43">
-        <v>67.96480911419161</v>
+        <v>67.96647584902836</v>
       </c>
       <c r="E43">
-        <v>15.241</v>
+        <v>15.942</v>
       </c>
       <c r="F43">
-        <v>28.741</v>
+        <v>29.442</v>
       </c>
       <c r="G43">
         <v>3.6</v>
@@ -4935,28 +4935,28 @@
         <v>7.12</v>
       </c>
       <c r="M43">
-        <v>1.6612298</v>
+        <v>1.7017476</v>
       </c>
       <c r="N43">
-        <v>5.4587702</v>
+        <v>5.4182524</v>
       </c>
       <c r="O43">
-        <v>0.54587702</v>
+        <v>0.54182524</v>
       </c>
       <c r="P43">
-        <v>4.91289318</v>
+        <v>4.87642716</v>
       </c>
       <c r="Q43">
-        <v>5.63289318</v>
+        <v>5.59642716</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1500612710851487</v>
+        <v>0.1517482860068817</v>
       </c>
       <c r="T43">
-        <v>1.612888704629599</v>
+        <v>1.638986288933771</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -4973,7 +4973,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.285981385597585</v>
+        <v>4.183934209750024</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4981,22 +4981,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1098624058839914</v>
+        <v>0.109860461827745</v>
       </c>
       <c r="C44">
-        <v>42.12447584902833</v>
+        <v>41.42514266561543</v>
       </c>
       <c r="D44">
-        <v>67.96647584902833</v>
+        <v>67.96814266561543</v>
       </c>
       <c r="E44">
-        <v>15.942</v>
+        <v>16.643</v>
       </c>
       <c r="F44">
-        <v>29.442</v>
+        <v>30.143</v>
       </c>
       <c r="G44">
         <v>3.6</v>
@@ -5017,28 +5017,28 @@
         <v>7.12</v>
       </c>
       <c r="M44">
-        <v>1.7017476</v>
+        <v>1.7422654</v>
       </c>
       <c r="N44">
-        <v>5.4182524</v>
+        <v>5.3777346</v>
       </c>
       <c r="O44">
-        <v>0.54182524</v>
+        <v>0.53777346</v>
       </c>
       <c r="P44">
-        <v>4.87642716</v>
+        <v>4.83996114</v>
       </c>
       <c r="Q44">
-        <v>5.59642716</v>
+        <v>5.55996114</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1517482860068817</v>
+        <v>0.1534944944346404</v>
       </c>
       <c r="T44">
-        <v>1.638986288933771</v>
+        <v>1.665999577950369</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.183934209750024</v>
+        <v>4.086633414174442</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5063,22 +5063,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.109860461827745</v>
+        <v>0.1112445177714987</v>
       </c>
       <c r="C45">
-        <v>41.42514266561543</v>
+        <v>39.55780030946781</v>
       </c>
       <c r="D45">
-        <v>67.96814266561543</v>
+        <v>66.80180030946781</v>
       </c>
       <c r="E45">
-        <v>16.643</v>
+        <v>17.344</v>
       </c>
       <c r="F45">
-        <v>30.143</v>
+        <v>30.844</v>
       </c>
       <c r="G45">
         <v>3.6</v>
@@ -5099,45 +5099,45 @@
         <v>7.12</v>
       </c>
       <c r="M45">
-        <v>1.7422654</v>
+        <v>1.8907372</v>
       </c>
       <c r="N45">
-        <v>5.3777346</v>
+        <v>5.229262800000001</v>
       </c>
       <c r="O45">
-        <v>0.53777346</v>
+        <v>0.5229262800000001</v>
       </c>
       <c r="P45">
-        <v>4.83996114</v>
+        <v>4.706336520000001</v>
       </c>
       <c r="Q45">
-        <v>5.55996114</v>
+        <v>5.42633652</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1534944944346404</v>
+        <v>0.1553030674491048</v>
       </c>
       <c r="T45">
-        <v>1.665999577950369</v>
+        <v>1.69397762728899</v>
       </c>
       <c r="U45">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V45">
         <v>0.1</v>
       </c>
       <c r="W45">
-        <v>0.05202</v>
+        <v>0.05517</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>4.086633414174442</v>
+        <v>3.765726934446522</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5145,22 +5145,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1112445177714987</v>
+        <v>0.1112740737152524</v>
       </c>
       <c r="C46">
-        <v>39.55780030946781</v>
+        <v>38.83232991999289</v>
       </c>
       <c r="D46">
-        <v>66.80180030946781</v>
+        <v>66.77732991999289</v>
       </c>
       <c r="E46">
-        <v>17.344</v>
+        <v>18.045</v>
       </c>
       <c r="F46">
-        <v>30.844</v>
+        <v>31.545</v>
       </c>
       <c r="G46">
         <v>3.6</v>
@@ -5181,28 +5181,28 @@
         <v>7.12</v>
       </c>
       <c r="M46">
-        <v>1.8907372</v>
+        <v>1.9337085</v>
       </c>
       <c r="N46">
-        <v>5.229262800000001</v>
+        <v>5.1862915</v>
       </c>
       <c r="O46">
-        <v>0.5229262800000001</v>
+        <v>0.5186291500000001</v>
       </c>
       <c r="P46">
-        <v>4.706336520000001</v>
+        <v>4.667662350000001</v>
       </c>
       <c r="Q46">
-        <v>5.42633652</v>
+        <v>5.38766235</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1553030674491048</v>
+        <v>0.1571774067550043</v>
       </c>
       <c r="T46">
-        <v>1.69397762728899</v>
+        <v>1.722973060239923</v>
       </c>
       <c r="U46">
         <v>0.0613</v>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.765726934446522</v>
+        <v>3.682044113681044</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1112740737152524</v>
+        <v>0.111303629659006</v>
       </c>
       <c r="C47">
-        <v>38.83232991999289</v>
+        <v>38.1068774516126</v>
       </c>
       <c r="D47">
-        <v>66.77732991999289</v>
+        <v>66.7528774516126</v>
       </c>
       <c r="E47">
-        <v>18.045</v>
+        <v>18.746</v>
       </c>
       <c r="F47">
-        <v>31.545</v>
+        <v>32.246</v>
       </c>
       <c r="G47">
         <v>3.6</v>
@@ -5263,28 +5263,28 @@
         <v>7.12</v>
       </c>
       <c r="M47">
-        <v>1.9337085</v>
+        <v>1.9766798</v>
       </c>
       <c r="N47">
-        <v>5.1862915</v>
+        <v>5.1433202</v>
       </c>
       <c r="O47">
-        <v>0.5186291500000001</v>
+        <v>0.51433202</v>
       </c>
       <c r="P47">
-        <v>4.667662350000001</v>
+        <v>4.628988179999999</v>
       </c>
       <c r="Q47">
-        <v>5.38766235</v>
+        <v>5.348988179999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1571774067550043</v>
+        <v>0.1591211660351963</v>
       </c>
       <c r="T47">
-        <v>1.722973060239923</v>
+        <v>1.753042398114965</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5301,7 +5301,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.682044113681044</v>
+        <v>3.601999676427107</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5309,22 +5309,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.111303629659006</v>
+        <v>0.1113331856027597</v>
       </c>
       <c r="C48">
-        <v>38.1068774516126</v>
+        <v>37.38144288464719</v>
       </c>
       <c r="D48">
-        <v>66.7528774516126</v>
+        <v>66.72844288464719</v>
       </c>
       <c r="E48">
-        <v>18.746</v>
+        <v>19.447</v>
       </c>
       <c r="F48">
-        <v>32.246</v>
+        <v>32.947</v>
       </c>
       <c r="G48">
         <v>3.6</v>
@@ -5345,28 +5345,28 @@
         <v>7.12</v>
       </c>
       <c r="M48">
-        <v>1.9766798</v>
+        <v>2.0196511</v>
       </c>
       <c r="N48">
-        <v>5.1433202</v>
+        <v>5.1003489</v>
       </c>
       <c r="O48">
-        <v>0.51433202</v>
+        <v>0.51003489</v>
       </c>
       <c r="P48">
-        <v>4.628988179999999</v>
+        <v>4.59031401</v>
       </c>
       <c r="Q48">
-        <v>5.348988179999999</v>
+        <v>5.31031401</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1591211660351963</v>
+        <v>0.1611382747221881</v>
       </c>
       <c r="T48">
-        <v>1.753042398114965</v>
+        <v>1.784246427985293</v>
       </c>
       <c r="U48">
         <v>0.0613</v>
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.601999676427107</v>
+        <v>3.525361385439297</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5391,22 +5391,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1113331856027597</v>
+        <v>0.1125723415465134</v>
       </c>
       <c r="C49">
-        <v>37.38144288464719</v>
+        <v>35.67185811495767</v>
       </c>
       <c r="D49">
-        <v>66.72844288464719</v>
+        <v>65.71985811495767</v>
       </c>
       <c r="E49">
-        <v>19.447</v>
+        <v>20.148</v>
       </c>
       <c r="F49">
-        <v>32.947</v>
+        <v>33.648</v>
       </c>
       <c r="G49">
         <v>3.6</v>
@@ -5427,45 +5427,45 @@
         <v>7.12</v>
       </c>
       <c r="M49">
-        <v>2.0196511</v>
+        <v>2.1568368</v>
       </c>
       <c r="N49">
-        <v>5.1003489</v>
+        <v>4.9631632</v>
       </c>
       <c r="O49">
-        <v>0.51003489</v>
+        <v>0.49631632</v>
       </c>
       <c r="P49">
-        <v>4.59031401</v>
+        <v>4.46684688</v>
       </c>
       <c r="Q49">
-        <v>5.31031401</v>
+        <v>5.18684688</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1611382747221881</v>
+        <v>0.1632329645125257</v>
       </c>
       <c r="T49">
-        <v>1.784246427985293</v>
+        <v>1.816650612850632</v>
       </c>
       <c r="U49">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V49">
         <v>0.1</v>
       </c>
       <c r="W49">
-        <v>0.05517</v>
+        <v>0.05769000000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>3.525361385439297</v>
+        <v>3.301130618691224</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5473,22 +5473,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1125723415465134</v>
+        <v>0.112627097490267</v>
       </c>
       <c r="C50">
-        <v>35.67185811495767</v>
+        <v>34.92699359597541</v>
       </c>
       <c r="D50">
-        <v>65.71985811495767</v>
+        <v>65.67599359597541</v>
       </c>
       <c r="E50">
-        <v>20.148</v>
+        <v>20.849</v>
       </c>
       <c r="F50">
-        <v>33.648</v>
+        <v>34.349</v>
       </c>
       <c r="G50">
         <v>3.6</v>
@@ -5509,28 +5509,28 @@
         <v>7.12</v>
       </c>
       <c r="M50">
-        <v>2.1568368</v>
+        <v>2.2017709</v>
       </c>
       <c r="N50">
-        <v>4.9631632</v>
+        <v>4.9182291</v>
       </c>
       <c r="O50">
-        <v>0.49631632</v>
+        <v>0.49182291</v>
       </c>
       <c r="P50">
-        <v>4.46684688</v>
+        <v>4.42640619</v>
       </c>
       <c r="Q50">
-        <v>5.18684688</v>
+        <v>5.14640619</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1632329645125257</v>
+        <v>0.1654097990005235</v>
       </c>
       <c r="T50">
-        <v>1.816650612850632</v>
+        <v>1.850325550063632</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5547,7 +5547,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.301130618691225</v>
+        <v>3.233760606064872</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5555,22 +5555,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.112627097490267</v>
+        <v>0.1126818534340207</v>
       </c>
       <c r="C51">
-        <v>34.92699359597541</v>
+        <v>34.18218759241621</v>
       </c>
       <c r="D51">
-        <v>65.67599359597541</v>
+        <v>65.63218759241622</v>
       </c>
       <c r="E51">
-        <v>20.849</v>
+        <v>21.55</v>
       </c>
       <c r="F51">
-        <v>34.349</v>
+        <v>35.05</v>
       </c>
       <c r="G51">
         <v>3.6</v>
@@ -5591,28 +5591,28 @@
         <v>7.12</v>
       </c>
       <c r="M51">
-        <v>2.2017709</v>
+        <v>2.246705</v>
       </c>
       <c r="N51">
-        <v>4.9182291</v>
+        <v>4.873295000000001</v>
       </c>
       <c r="O51">
-        <v>0.49182291</v>
+        <v>0.4873295000000001</v>
       </c>
       <c r="P51">
-        <v>4.42640619</v>
+        <v>4.3859655</v>
       </c>
       <c r="Q51">
-        <v>5.14640619</v>
+        <v>5.1059655</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1654097990005235</v>
+        <v>0.1676737068680413</v>
       </c>
       <c r="T51">
-        <v>1.850325550063632</v>
+        <v>1.885347484765151</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5629,7 +5629,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.233760606064872</v>
+        <v>3.169085393943575</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5637,22 +5637,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1126818534340207</v>
+        <v>0.1127366093777743</v>
       </c>
       <c r="C52">
-        <v>34.18218759241621</v>
+        <v>33.43743998726841</v>
       </c>
       <c r="D52">
-        <v>65.63218759241622</v>
+        <v>65.58843998726842</v>
       </c>
       <c r="E52">
-        <v>21.55</v>
+        <v>22.251</v>
       </c>
       <c r="F52">
-        <v>35.05</v>
+        <v>35.751</v>
       </c>
       <c r="G52">
         <v>3.6</v>
@@ -5673,28 +5673,28 @@
         <v>7.12</v>
       </c>
       <c r="M52">
-        <v>2.246705</v>
+        <v>2.2916391</v>
       </c>
       <c r="N52">
-        <v>4.873295000000001</v>
+        <v>4.8283609</v>
       </c>
       <c r="O52">
-        <v>0.4873295000000001</v>
+        <v>0.48283609</v>
       </c>
       <c r="P52">
-        <v>4.3859655</v>
+        <v>4.34552481</v>
       </c>
       <c r="Q52">
-        <v>5.1059655</v>
+        <v>5.065524809999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1676737068680413</v>
+        <v>0.1700300191383149</v>
       </c>
       <c r="T52">
-        <v>1.885347484765151</v>
+        <v>1.921798886189182</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.169085393943575</v>
+        <v>3.106946464650564</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5719,22 +5719,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1127366093777743</v>
+        <v>0.112791365321528</v>
       </c>
       <c r="C53">
-        <v>33.43743998726841</v>
+        <v>32.69275066383219</v>
       </c>
       <c r="D53">
-        <v>65.58843998726842</v>
+        <v>65.54475066383219</v>
       </c>
       <c r="E53">
-        <v>22.251</v>
+        <v>22.952</v>
       </c>
       <c r="F53">
-        <v>35.751</v>
+        <v>36.452</v>
       </c>
       <c r="G53">
         <v>3.6</v>
@@ -5755,28 +5755,28 @@
         <v>7.12</v>
       </c>
       <c r="M53">
-        <v>2.2916391</v>
+        <v>2.3365732</v>
       </c>
       <c r="N53">
-        <v>4.8283609</v>
+        <v>4.7834268</v>
       </c>
       <c r="O53">
-        <v>0.48283609</v>
+        <v>0.47834268</v>
       </c>
       <c r="P53">
-        <v>4.34552481</v>
+        <v>4.30508412</v>
       </c>
       <c r="Q53">
-        <v>5.065524809999999</v>
+        <v>5.02508412</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1700300191383149</v>
+        <v>0.1724845110865167</v>
       </c>
       <c r="T53">
-        <v>1.921798886189182</v>
+        <v>1.959769096005881</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.106946464650564</v>
+        <v>3.047197494176515</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5801,22 +5801,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.112791365321528</v>
+        <v>0.1165667212652817</v>
       </c>
       <c r="C54">
-        <v>32.69275066383219</v>
+        <v>29.11361735505985</v>
       </c>
       <c r="D54">
-        <v>65.54475066383219</v>
+        <v>62.66661735505986</v>
       </c>
       <c r="E54">
-        <v>22.952</v>
+        <v>23.653</v>
       </c>
       <c r="F54">
-        <v>36.452</v>
+        <v>37.153</v>
       </c>
       <c r="G54">
         <v>3.6</v>
@@ -5837,45 +5837,45 @@
         <v>7.12</v>
       </c>
       <c r="M54">
-        <v>2.3365732</v>
+        <v>2.6713007</v>
       </c>
       <c r="N54">
-        <v>4.7834268</v>
+        <v>4.448699299999999</v>
       </c>
       <c r="O54">
-        <v>0.47834268</v>
+        <v>0.44486993</v>
       </c>
       <c r="P54">
-        <v>4.30508412</v>
+        <v>4.003829369999999</v>
       </c>
       <c r="Q54">
-        <v>5.02508412</v>
+        <v>4.723829369999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1724845110865167</v>
+        <v>0.1750434495005993</v>
       </c>
       <c r="T54">
-        <v>1.959769096005881</v>
+        <v>1.999355059431801</v>
       </c>
       <c r="U54">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V54">
         <v>0.1</v>
       </c>
       <c r="W54">
-        <v>0.05769000000000001</v>
+        <v>0.06471</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>3.047197494176515</v>
+        <v>2.665368223053286</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5883,22 +5883,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1165667212652817</v>
+        <v>0.1166916772090353</v>
       </c>
       <c r="C55">
-        <v>29.11361735505985</v>
+        <v>28.32167262633605</v>
       </c>
       <c r="D55">
-        <v>62.66661735505986</v>
+        <v>62.57567262633606</v>
       </c>
       <c r="E55">
-        <v>23.653</v>
+        <v>24.354</v>
       </c>
       <c r="F55">
-        <v>37.153</v>
+        <v>37.854</v>
       </c>
       <c r="G55">
         <v>3.6</v>
@@ -5919,28 +5919,28 @@
         <v>7.12</v>
       </c>
       <c r="M55">
-        <v>2.6713007</v>
+        <v>2.7217026</v>
       </c>
       <c r="N55">
-        <v>4.448699299999999</v>
+        <v>4.398297400000001</v>
       </c>
       <c r="O55">
-        <v>0.44486993</v>
+        <v>0.4398297400000001</v>
       </c>
       <c r="P55">
-        <v>4.003829369999999</v>
+        <v>3.958467660000001</v>
       </c>
       <c r="Q55">
-        <v>4.723829369999999</v>
+        <v>4.678467660000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1750434495005993</v>
+        <v>0.1777136461065985</v>
       </c>
       <c r="T55">
-        <v>1.999355059431801</v>
+        <v>2.040662151702327</v>
       </c>
       <c r="U55">
         <v>0.07190000000000001</v>
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.665368223053286</v>
+        <v>2.616009552256004</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5965,22 +5965,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1166916772090353</v>
+        <v>0.116816633152789</v>
       </c>
       <c r="C56">
-        <v>28.32167262633605</v>
+        <v>27.52999148158232</v>
       </c>
       <c r="D56">
-        <v>62.57567262633606</v>
+        <v>62.48499148158232</v>
       </c>
       <c r="E56">
-        <v>24.354</v>
+        <v>25.055</v>
       </c>
       <c r="F56">
-        <v>37.854</v>
+        <v>38.555</v>
       </c>
       <c r="G56">
         <v>3.6</v>
@@ -6001,28 +6001,28 @@
         <v>7.12</v>
       </c>
       <c r="M56">
-        <v>2.7217026</v>
+        <v>2.7721045</v>
       </c>
       <c r="N56">
-        <v>4.398297400000001</v>
+        <v>4.3478955</v>
       </c>
       <c r="O56">
-        <v>0.4398297400000001</v>
+        <v>0.43478955</v>
       </c>
       <c r="P56">
-        <v>3.958467660000001</v>
+        <v>3.91310595</v>
       </c>
       <c r="Q56">
-        <v>4.678467660000001</v>
+        <v>4.63310595</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1777136461065985</v>
+        <v>0.1805025181173089</v>
       </c>
       <c r="T56">
-        <v>2.040662151702327</v>
+        <v>2.083805114740431</v>
       </c>
       <c r="U56">
         <v>0.07190000000000001</v>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.616009552256004</v>
+        <v>2.568445742214985</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6047,22 +6047,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.116816633152789</v>
+        <v>0.1169415890965426</v>
       </c>
       <c r="C57">
-        <v>27.52999148158232</v>
+        <v>26.73857277654368</v>
       </c>
       <c r="D57">
-        <v>62.48499148158232</v>
+        <v>62.39457277654368</v>
       </c>
       <c r="E57">
-        <v>25.055</v>
+        <v>25.756</v>
       </c>
       <c r="F57">
-        <v>38.555</v>
+        <v>39.256</v>
       </c>
       <c r="G57">
         <v>3.6</v>
@@ -6083,28 +6083,28 @@
         <v>7.12</v>
       </c>
       <c r="M57">
-        <v>2.7721045</v>
+        <v>2.8225064</v>
       </c>
       <c r="N57">
-        <v>4.3478955</v>
+        <v>4.297493599999999</v>
       </c>
       <c r="O57">
-        <v>0.43478955</v>
+        <v>0.42974936</v>
       </c>
       <c r="P57">
-        <v>3.91310595</v>
+        <v>3.86774424</v>
       </c>
       <c r="Q57">
-        <v>4.63310595</v>
+        <v>4.587744239999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1805025181173089</v>
+        <v>0.1834181570375969</v>
       </c>
       <c r="T57">
-        <v>2.083805114740431</v>
+        <v>2.128909121552994</v>
       </c>
       <c r="U57">
         <v>0.07190000000000001</v>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.568445742214985</v>
+        <v>2.522580639675431</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6129,22 +6129,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1169415890965426</v>
+        <v>0.1190672450402963</v>
       </c>
       <c r="C58">
-        <v>26.73857277654368</v>
+        <v>24.53856365651081</v>
       </c>
       <c r="D58">
-        <v>62.39457277654368</v>
+        <v>60.89556365651081</v>
       </c>
       <c r="E58">
-        <v>25.756</v>
+        <v>26.457</v>
       </c>
       <c r="F58">
-        <v>39.256</v>
+        <v>39.957</v>
       </c>
       <c r="G58">
         <v>3.6</v>
@@ -6165,45 +6165,45 @@
         <v>7.12</v>
       </c>
       <c r="M58">
-        <v>2.8225064</v>
+        <v>3.0287406</v>
       </c>
       <c r="N58">
-        <v>4.297493599999999</v>
+        <v>4.0912594</v>
       </c>
       <c r="O58">
-        <v>0.42974936</v>
+        <v>0.40912594</v>
       </c>
       <c r="P58">
-        <v>3.86774424</v>
+        <v>3.68213346</v>
       </c>
       <c r="Q58">
-        <v>4.587744239999999</v>
+        <v>4.40213346</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1834181570375969</v>
+        <v>0.1864694070704566</v>
       </c>
       <c r="T58">
-        <v>2.128909121552994</v>
+        <v>2.176110989147538</v>
       </c>
       <c r="U58">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V58">
         <v>0.1</v>
       </c>
       <c r="W58">
-        <v>0.06471</v>
+        <v>0.06822</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.522580639675431</v>
+        <v>2.350812083411831</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6211,22 +6211,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1190672450402963</v>
+        <v>0.11922730098405</v>
       </c>
       <c r="C59">
-        <v>24.53856365651081</v>
+        <v>23.7276030758254</v>
       </c>
       <c r="D59">
-        <v>60.89556365651081</v>
+        <v>60.7856030758254</v>
       </c>
       <c r="E59">
-        <v>26.457</v>
+        <v>27.158</v>
       </c>
       <c r="F59">
-        <v>39.957</v>
+        <v>40.658</v>
       </c>
       <c r="G59">
         <v>3.6</v>
@@ -6247,28 +6247,28 @@
         <v>7.12</v>
       </c>
       <c r="M59">
-        <v>3.0287406</v>
+        <v>3.081876400000001</v>
       </c>
       <c r="N59">
-        <v>4.0912594</v>
+        <v>4.0381236</v>
       </c>
       <c r="O59">
-        <v>0.40912594</v>
+        <v>0.40381236</v>
       </c>
       <c r="P59">
-        <v>3.68213346</v>
+        <v>3.63431124</v>
       </c>
       <c r="Q59">
-        <v>4.40213346</v>
+        <v>4.354311239999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1864694070704566</v>
+        <v>0.1896659547239285</v>
       </c>
       <c r="T59">
-        <v>2.176110989147538</v>
+        <v>2.225560564722773</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6285,7 +6285,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.350812083411831</v>
+        <v>2.310280840594386</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.11922730098405</v>
+        <v>0.1193873569278036</v>
       </c>
       <c r="C60">
-        <v>23.72760307582539</v>
+        <v>22.91703889626777</v>
       </c>
       <c r="D60">
-        <v>60.78560307582539</v>
+        <v>60.67603889626777</v>
       </c>
       <c r="E60">
-        <v>27.15799999999999</v>
+        <v>27.85899999999999</v>
       </c>
       <c r="F60">
-        <v>40.65799999999999</v>
+        <v>41.35899999999999</v>
       </c>
       <c r="G60">
         <v>3.6</v>
@@ -6329,28 +6329,28 @@
         <v>7.12</v>
       </c>
       <c r="M60">
-        <v>3.0818764</v>
+        <v>3.1350122</v>
       </c>
       <c r="N60">
-        <v>4.0381236</v>
+        <v>3.9849878</v>
       </c>
       <c r="O60">
-        <v>0.4038123600000001</v>
+        <v>0.3984987800000001</v>
       </c>
       <c r="P60">
-        <v>3.634311240000001</v>
+        <v>3.58648902</v>
       </c>
       <c r="Q60">
-        <v>4.35431124</v>
+        <v>4.30648902</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1896659547239285</v>
+        <v>0.1930184315312284</v>
       </c>
       <c r="T60">
-        <v>2.225560564722773</v>
+        <v>2.277422314716313</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.310280840594386</v>
+        <v>2.27112353821143</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6375,22 +6375,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1193873569278036</v>
+        <v>0.1195474128715573</v>
       </c>
       <c r="C61">
-        <v>22.91703889626777</v>
+        <v>22.10686897819209</v>
       </c>
       <c r="D61">
-        <v>60.67603889626777</v>
+        <v>60.56686897819209</v>
       </c>
       <c r="E61">
-        <v>27.85899999999999</v>
+        <v>28.56</v>
       </c>
       <c r="F61">
-        <v>41.35899999999999</v>
+        <v>42.06</v>
       </c>
       <c r="G61">
         <v>3.6</v>
@@ -6411,28 +6411,28 @@
         <v>7.12</v>
       </c>
       <c r="M61">
-        <v>3.1350122</v>
+        <v>3.188148</v>
       </c>
       <c r="N61">
-        <v>3.9849878</v>
+        <v>3.931852</v>
       </c>
       <c r="O61">
-        <v>0.3984987800000001</v>
+        <v>0.3931852</v>
       </c>
       <c r="P61">
-        <v>3.58648902</v>
+        <v>3.5386668</v>
       </c>
       <c r="Q61">
-        <v>4.30648902</v>
+        <v>4.2586668</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1930184315312284</v>
+        <v>0.1965385321788932</v>
       </c>
       <c r="T61">
-        <v>2.277422314716313</v>
+        <v>2.331877152209529</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6449,7 +6449,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.27112353821143</v>
+        <v>2.23327147924124</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6457,22 +6457,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1195474128715573</v>
+        <v>0.119707468815311</v>
       </c>
       <c r="C62">
-        <v>22.10686897819209</v>
+        <v>21.2970911973236</v>
       </c>
       <c r="D62">
-        <v>60.56686897819209</v>
+        <v>60.4580911973236</v>
       </c>
       <c r="E62">
-        <v>28.56</v>
+        <v>29.261</v>
       </c>
       <c r="F62">
-        <v>42.06</v>
+        <v>42.761</v>
       </c>
       <c r="G62">
         <v>3.6</v>
@@ -6493,28 +6493,28 @@
         <v>7.12</v>
       </c>
       <c r="M62">
-        <v>3.188148</v>
+        <v>3.2412838</v>
       </c>
       <c r="N62">
-        <v>3.931852</v>
+        <v>3.8787162</v>
       </c>
       <c r="O62">
-        <v>0.3931852</v>
+        <v>0.38787162</v>
       </c>
       <c r="P62">
-        <v>3.5386668</v>
+        <v>3.49084458</v>
       </c>
       <c r="Q62">
-        <v>4.2586668</v>
+        <v>4.21084458</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1965385321788932</v>
+        <v>0.2002391508084897</v>
       </c>
       <c r="T62">
-        <v>2.331877152209529</v>
+        <v>2.38912454547163</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.23327147924124</v>
+        <v>2.196660471384826</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6539,22 +6539,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.119707468815311</v>
+        <v>0.1198675247590646</v>
       </c>
       <c r="C63">
-        <v>21.2970911973236</v>
+        <v>20.48770344462108</v>
       </c>
       <c r="D63">
-        <v>60.4580911973236</v>
+        <v>60.34970344462107</v>
       </c>
       <c r="E63">
-        <v>29.261</v>
+        <v>29.962</v>
       </c>
       <c r="F63">
-        <v>42.761</v>
+        <v>43.462</v>
       </c>
       <c r="G63">
         <v>3.6</v>
@@ -6575,28 +6575,28 @@
         <v>7.12</v>
       </c>
       <c r="M63">
-        <v>3.2412838</v>
+        <v>3.2944196</v>
       </c>
       <c r="N63">
-        <v>3.8787162</v>
+        <v>3.8255804</v>
       </c>
       <c r="O63">
-        <v>0.38787162</v>
+        <v>0.38255804</v>
       </c>
       <c r="P63">
-        <v>3.49084458</v>
+        <v>3.44302236</v>
       </c>
       <c r="Q63">
-        <v>4.21084458</v>
+        <v>4.16302236</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2002391508084897</v>
+        <v>0.2041345388396437</v>
       </c>
       <c r="T63">
-        <v>2.38912454547163</v>
+        <v>2.449384959431734</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6613,7 +6613,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.196660471384826</v>
+        <v>2.161230463781845</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6621,22 +6621,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1198675247590646</v>
+        <v>0.1200275807028183</v>
       </c>
       <c r="C64">
-        <v>20.48770344462108</v>
+        <v>19.67870362614023</v>
       </c>
       <c r="D64">
-        <v>60.34970344462107</v>
+        <v>60.24170362614022</v>
       </c>
       <c r="E64">
-        <v>29.962</v>
+        <v>30.663</v>
       </c>
       <c r="F64">
-        <v>43.462</v>
+        <v>44.163</v>
       </c>
       <c r="G64">
         <v>3.6</v>
@@ -6657,28 +6657,28 @@
         <v>7.12</v>
       </c>
       <c r="M64">
-        <v>3.2944196</v>
+        <v>3.3475554</v>
       </c>
       <c r="N64">
-        <v>3.8255804</v>
+        <v>3.7724446</v>
       </c>
       <c r="O64">
-        <v>0.38255804</v>
+        <v>0.37724446</v>
       </c>
       <c r="P64">
-        <v>3.44302236</v>
+        <v>3.39520014</v>
       </c>
       <c r="Q64">
-        <v>4.16302236</v>
+        <v>4.11520014</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2041345388396437</v>
+        <v>0.2082404883859953</v>
       </c>
       <c r="T64">
-        <v>2.449384959431734</v>
+        <v>2.512902693065358</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6695,7 +6695,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.161230463781845</v>
+        <v>2.12692521832499</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6703,22 +6703,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1200275807028183</v>
+        <v>0.1201876366465719</v>
       </c>
       <c r="C65">
-        <v>19.67870362614023</v>
+        <v>18.87008966289905</v>
       </c>
       <c r="D65">
-        <v>60.24170362614022</v>
+        <v>60.13408966289905</v>
       </c>
       <c r="E65">
-        <v>30.663</v>
+        <v>31.364</v>
       </c>
       <c r="F65">
-        <v>44.163</v>
+        <v>44.864</v>
       </c>
       <c r="G65">
         <v>3.6</v>
@@ -6739,28 +6739,28 @@
         <v>7.12</v>
       </c>
       <c r="M65">
-        <v>3.3475554</v>
+        <v>3.4006912</v>
       </c>
       <c r="N65">
-        <v>3.7724446</v>
+        <v>3.7193088</v>
       </c>
       <c r="O65">
-        <v>0.37724446</v>
+        <v>0.37193088</v>
       </c>
       <c r="P65">
-        <v>3.39520014</v>
+        <v>3.34737792</v>
       </c>
       <c r="Q65">
-        <v>4.11520014</v>
+        <v>4.06737792</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2082404883859953</v>
+        <v>0.2125745462404776</v>
       </c>
       <c r="T65">
-        <v>2.512902693065358</v>
+        <v>2.579949189678628</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.12692521832499</v>
+        <v>2.093692011788662</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6785,22 +6785,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1201876366465719</v>
+        <v>0.1203476925903256</v>
       </c>
       <c r="C66">
-        <v>18.87008966289905</v>
+        <v>18.06185949074442</v>
       </c>
       <c r="D66">
-        <v>60.13408966289905</v>
+        <v>60.02685949074441</v>
       </c>
       <c r="E66">
-        <v>31.364</v>
+        <v>32.065</v>
       </c>
       <c r="F66">
-        <v>44.864</v>
+        <v>45.565</v>
       </c>
       <c r="G66">
         <v>3.6</v>
@@ -6821,28 +6821,28 @@
         <v>7.12</v>
       </c>
       <c r="M66">
-        <v>3.4006912</v>
+        <v>3.453827</v>
       </c>
       <c r="N66">
-        <v>3.7193088</v>
+        <v>3.666173</v>
       </c>
       <c r="O66">
-        <v>0.37193088</v>
+        <v>0.3666173</v>
       </c>
       <c r="P66">
-        <v>3.34737792</v>
+        <v>3.2995557</v>
       </c>
       <c r="Q66">
-        <v>4.06737792</v>
+        <v>4.0195557</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2125745462404776</v>
+        <v>0.2171562645437874</v>
       </c>
       <c r="T66">
-        <v>2.579949189678628</v>
+        <v>2.6508269146698</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6859,7 +6859,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.093692011788662</v>
+        <v>2.061481365453452</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6867,22 +6867,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1203476925903256</v>
+        <v>0.1205077485340793</v>
       </c>
       <c r="C67">
-        <v>18.06185949074442</v>
+        <v>17.25401106022</v>
       </c>
       <c r="D67">
-        <v>60.02685949074441</v>
+        <v>59.92001106022</v>
       </c>
       <c r="E67">
-        <v>32.065</v>
+        <v>32.766</v>
       </c>
       <c r="F67">
-        <v>45.565</v>
+        <v>46.266</v>
       </c>
       <c r="G67">
         <v>3.6</v>
@@ -6903,28 +6903,28 @@
         <v>7.12</v>
       </c>
       <c r="M67">
-        <v>3.453827</v>
+        <v>3.5069628</v>
       </c>
       <c r="N67">
-        <v>3.666173</v>
+        <v>3.6130372</v>
       </c>
       <c r="O67">
-        <v>0.3666173</v>
+        <v>0.36130372</v>
       </c>
       <c r="P67">
-        <v>3.2995557</v>
+        <v>3.25173348</v>
       </c>
       <c r="Q67">
-        <v>4.0195557</v>
+        <v>3.97173348</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2171562645437874</v>
+        <v>0.2220074956884684</v>
       </c>
       <c r="T67">
-        <v>2.6508269146698</v>
+        <v>2.725873917601628</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.061481365453452</v>
+        <v>2.030246799310218</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6949,22 +6949,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1205077485340793</v>
+        <v>0.1292304044778329</v>
       </c>
       <c r="C68">
-        <v>17.25401106022</v>
+        <v>11.25439725769422</v>
       </c>
       <c r="D68">
-        <v>59.92001106022</v>
+        <v>54.62139725769422</v>
       </c>
       <c r="E68">
-        <v>32.766</v>
+        <v>33.467</v>
       </c>
       <c r="F68">
-        <v>46.266</v>
+        <v>46.967</v>
       </c>
       <c r="G68">
         <v>3.6</v>
@@ -6985,45 +6985,45 @@
         <v>7.12</v>
       </c>
       <c r="M68">
-        <v>3.5069628</v>
+        <v>4.22703</v>
       </c>
       <c r="N68">
-        <v>3.6130372</v>
+        <v>2.89297</v>
       </c>
       <c r="O68">
-        <v>0.36130372</v>
+        <v>0.289297</v>
       </c>
       <c r="P68">
-        <v>3.25173348</v>
+        <v>2.603673</v>
       </c>
       <c r="Q68">
-        <v>3.97173348</v>
+        <v>3.323673</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2220074956884684</v>
+        <v>0.227152740841918</v>
       </c>
       <c r="T68">
-        <v>2.725873917601628</v>
+        <v>2.805469223741446</v>
       </c>
       <c r="U68">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V68">
         <v>0.1</v>
       </c>
       <c r="W68">
-        <v>0.06822</v>
+        <v>0.081</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y68">
-        <v>2.030246799310218</v>
+        <v>1.684397792303343</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7031,22 +7031,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1292304044778329</v>
+        <v>0.1295182604215866</v>
       </c>
       <c r="C69">
-        <v>11.25439725769422</v>
+        <v>10.39446424046639</v>
       </c>
       <c r="D69">
-        <v>54.62139725769422</v>
+        <v>54.46246424046639</v>
       </c>
       <c r="E69">
-        <v>33.467</v>
+        <v>34.168</v>
       </c>
       <c r="F69">
-        <v>46.967</v>
+        <v>47.668</v>
       </c>
       <c r="G69">
         <v>3.6</v>
@@ -7067,28 +7067,28 @@
         <v>7.12</v>
       </c>
       <c r="M69">
-        <v>4.22703</v>
+        <v>4.29012</v>
       </c>
       <c r="N69">
-        <v>2.89297</v>
+        <v>2.82988</v>
       </c>
       <c r="O69">
-        <v>0.289297</v>
+        <v>0.282988</v>
       </c>
       <c r="P69">
-        <v>2.603673</v>
+        <v>2.546892</v>
       </c>
       <c r="Q69">
-        <v>3.323673</v>
+        <v>3.266892</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.227152740841918</v>
+        <v>0.2326195638174581</v>
       </c>
       <c r="T69">
-        <v>2.805469223741446</v>
+        <v>2.890039236515002</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.684397792303343</v>
+        <v>1.659627236534176</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7113,22 +7113,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1295182604215866</v>
+        <v>0.1298061163653403</v>
       </c>
       <c r="C70">
-        <v>10.39446424046639</v>
+        <v>9.535453441262348</v>
       </c>
       <c r="D70">
-        <v>54.46246424046639</v>
+        <v>54.30445344126235</v>
       </c>
       <c r="E70">
-        <v>34.168</v>
+        <v>34.869</v>
       </c>
       <c r="F70">
-        <v>47.668</v>
+        <v>48.369</v>
       </c>
       <c r="G70">
         <v>3.6</v>
@@ -7149,28 +7149,28 @@
         <v>7.12</v>
       </c>
       <c r="M70">
-        <v>4.29012</v>
+        <v>4.35321</v>
       </c>
       <c r="N70">
-        <v>2.82988</v>
+        <v>2.76679</v>
       </c>
       <c r="O70">
-        <v>0.282988</v>
+        <v>0.2766790000000001</v>
       </c>
       <c r="P70">
-        <v>2.546892</v>
+        <v>2.490111</v>
       </c>
       <c r="Q70">
-        <v>3.266892</v>
+        <v>3.210111</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2326195638174581</v>
+        <v>0.2384390850494847</v>
       </c>
       <c r="T70">
-        <v>2.890039236515002</v>
+        <v>2.980065379144918</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.659627236534176</v>
+        <v>1.635574667888753</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7195,22 +7195,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1298061163653403</v>
+        <v>0.1300939723090939</v>
       </c>
       <c r="C71">
-        <v>9.535453441262348</v>
+        <v>8.67735685646776</v>
       </c>
       <c r="D71">
-        <v>54.30445344126235</v>
+        <v>54.14735685646776</v>
       </c>
       <c r="E71">
-        <v>34.869</v>
+        <v>35.57</v>
       </c>
       <c r="F71">
-        <v>48.369</v>
+        <v>49.07</v>
       </c>
       <c r="G71">
         <v>3.6</v>
@@ -7231,28 +7231,28 @@
         <v>7.12</v>
       </c>
       <c r="M71">
-        <v>4.35321</v>
+        <v>4.4163</v>
       </c>
       <c r="N71">
-        <v>2.76679</v>
+        <v>2.7037</v>
       </c>
       <c r="O71">
-        <v>0.2766790000000001</v>
+        <v>0.2703700000000001</v>
       </c>
       <c r="P71">
-        <v>2.490111</v>
+        <v>2.43333</v>
       </c>
       <c r="Q71">
-        <v>3.210111</v>
+        <v>3.15333</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2384390850494847</v>
+        <v>0.2446465743636464</v>
       </c>
       <c r="T71">
-        <v>2.980065379144918</v>
+        <v>3.076093264616827</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.635574667888753</v>
+        <v>1.612209315490343</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7277,22 +7277,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1300939723090939</v>
+        <v>0.1303818282528476</v>
       </c>
       <c r="C72">
-        <v>8.67735685646776</v>
+        <v>7.820166574815175</v>
       </c>
       <c r="D72">
-        <v>54.14735685646776</v>
+        <v>53.99116657481517</v>
       </c>
       <c r="E72">
-        <v>35.57</v>
+        <v>36.271</v>
       </c>
       <c r="F72">
-        <v>49.07</v>
+        <v>49.771</v>
       </c>
       <c r="G72">
         <v>3.6</v>
@@ -7313,28 +7313,28 @@
         <v>7.12</v>
       </c>
       <c r="M72">
-        <v>4.4163</v>
+        <v>4.47939</v>
       </c>
       <c r="N72">
-        <v>2.7037</v>
+        <v>2.640610000000001</v>
       </c>
       <c r="O72">
-        <v>0.2703700000000001</v>
+        <v>0.264061</v>
       </c>
       <c r="P72">
-        <v>2.43333</v>
+        <v>2.376549000000001</v>
       </c>
       <c r="Q72">
-        <v>3.15333</v>
+        <v>3.096549</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2446465743636464</v>
+        <v>0.2512821663891296</v>
       </c>
       <c r="T72">
-        <v>3.076093264616827</v>
+        <v>3.178743762879903</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.612209315490343</v>
+        <v>1.589502142032732</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7359,22 +7359,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1303818282528476</v>
+        <v>0.1306696841966012</v>
       </c>
       <c r="C73">
-        <v>7.820166574815183</v>
+        <v>6.963874776056201</v>
       </c>
       <c r="D73">
-        <v>53.99116657481517</v>
+        <v>53.83587477605619</v>
       </c>
       <c r="E73">
-        <v>36.27099999999999</v>
+        <v>36.97199999999999</v>
       </c>
       <c r="F73">
-        <v>49.77099999999999</v>
+        <v>50.47199999999999</v>
       </c>
       <c r="G73">
         <v>3.6</v>
@@ -7395,28 +7395,28 @@
         <v>7.12</v>
       </c>
       <c r="M73">
-        <v>4.47939</v>
+        <v>4.542479999999999</v>
       </c>
       <c r="N73">
-        <v>2.640610000000001</v>
+        <v>2.577520000000001</v>
       </c>
       <c r="O73">
-        <v>0.264061</v>
+        <v>0.2577520000000001</v>
       </c>
       <c r="P73">
-        <v>2.376549000000001</v>
+        <v>2.319768000000001</v>
       </c>
       <c r="Q73">
-        <v>3.096549</v>
+        <v>3.039768</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2512821663891296</v>
+        <v>0.2583917292735758</v>
       </c>
       <c r="T73">
-        <v>3.178743762879902</v>
+        <v>3.288726439590339</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7433,7 +7433,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.589502142032732</v>
+        <v>1.567425723393389</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7441,22 +7441,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1306696841966012</v>
+        <v>0.1309575401403549</v>
       </c>
       <c r="C74">
-        <v>6.963874776056201</v>
+        <v>6.10847372965614</v>
       </c>
       <c r="D74">
-        <v>53.83587477605619</v>
+        <v>53.68147372965613</v>
       </c>
       <c r="E74">
-        <v>36.97199999999999</v>
+        <v>37.67299999999999</v>
       </c>
       <c r="F74">
-        <v>50.47199999999999</v>
+        <v>51.17299999999999</v>
       </c>
       <c r="G74">
         <v>3.6</v>
@@ -7477,28 +7477,28 @@
         <v>7.12</v>
       </c>
       <c r="M74">
-        <v>4.542479999999999</v>
+        <v>4.605569999999999</v>
       </c>
       <c r="N74">
-        <v>2.577520000000001</v>
+        <v>2.514430000000001</v>
       </c>
       <c r="O74">
-        <v>0.2577520000000001</v>
+        <v>0.2514430000000001</v>
       </c>
       <c r="P74">
-        <v>2.319768000000001</v>
+        <v>2.262987000000001</v>
       </c>
       <c r="Q74">
-        <v>3.039768</v>
+        <v>2.982987</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2583917292735758</v>
+        <v>0.2660279264457589</v>
       </c>
       <c r="T74">
-        <v>3.288726439590339</v>
+        <v>3.406855981242291</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.567425723393389</v>
+        <v>1.545954138141425</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7523,22 +7523,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1309575401403549</v>
+        <v>0.1312453960841086</v>
       </c>
       <c r="C75">
-        <v>6.10847372965614</v>
+        <v>5.25395579351126</v>
       </c>
       <c r="D75">
-        <v>53.68147372965613</v>
+        <v>53.52795579351125</v>
       </c>
       <c r="E75">
-        <v>37.67299999999999</v>
+        <v>38.374</v>
       </c>
       <c r="F75">
-        <v>51.17299999999999</v>
+        <v>51.874</v>
       </c>
       <c r="G75">
         <v>3.6</v>
@@ -7559,28 +7559,28 @@
         <v>7.12</v>
       </c>
       <c r="M75">
-        <v>4.605569999999999</v>
+        <v>4.668659999999999</v>
       </c>
       <c r="N75">
-        <v>2.514430000000001</v>
+        <v>2.451340000000001</v>
       </c>
       <c r="O75">
-        <v>0.2514430000000001</v>
+        <v>0.2451340000000001</v>
       </c>
       <c r="P75">
-        <v>2.262987000000001</v>
+        <v>2.206206000000001</v>
       </c>
       <c r="Q75">
-        <v>2.982987</v>
+        <v>2.926206000000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2660279264457589</v>
+        <v>0.2742515234004175</v>
       </c>
       <c r="T75">
-        <v>3.406855981242291</v>
+        <v>3.534072410713624</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7597,7 +7597,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.545954138141425</v>
+        <v>1.525062866004379</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7605,22 +7605,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1312453960841086</v>
+        <v>0.1315332520278622</v>
       </c>
       <c r="C76">
-        <v>5.25395579351126</v>
+        <v>4.400313412687886</v>
       </c>
       <c r="D76">
-        <v>53.52795579351125</v>
+        <v>53.37531341268788</v>
       </c>
       <c r="E76">
-        <v>38.374</v>
+        <v>39.075</v>
       </c>
       <c r="F76">
-        <v>51.874</v>
+        <v>52.575</v>
       </c>
       <c r="G76">
         <v>3.6</v>
@@ -7641,28 +7641,28 @@
         <v>7.12</v>
       </c>
       <c r="M76">
-        <v>4.668659999999999</v>
+        <v>4.731749999999999</v>
       </c>
       <c r="N76">
-        <v>2.451340000000001</v>
+        <v>2.388250000000001</v>
       </c>
       <c r="O76">
-        <v>0.2451340000000001</v>
+        <v>0.2388250000000001</v>
       </c>
       <c r="P76">
-        <v>2.206206000000001</v>
+        <v>2.149425000000001</v>
       </c>
       <c r="Q76">
-        <v>2.926206000000001</v>
+        <v>2.869425000000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2742515234004175</v>
+        <v>0.2831330081114489</v>
       </c>
       <c r="T76">
-        <v>3.534072410713624</v>
+        <v>3.671466154542664</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7679,7 +7679,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.525062866004379</v>
+        <v>1.504728694457653</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7687,22 +7687,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1315332520278622</v>
+        <v>0.1721090860356816</v>
       </c>
       <c r="C77">
-        <v>4.400313412687886</v>
+        <v>-11.60417458325575</v>
       </c>
       <c r="D77">
-        <v>53.37531341268788</v>
+        <v>38.07182541674425</v>
       </c>
       <c r="E77">
-        <v>39.075</v>
+        <v>39.776</v>
       </c>
       <c r="F77">
-        <v>52.575</v>
+        <v>53.276</v>
       </c>
       <c r="G77">
         <v>3.6</v>
@@ -7723,45 +7723,45 @@
         <v>7.12</v>
       </c>
       <c r="M77">
-        <v>4.731749999999999</v>
+        <v>7.8209168</v>
       </c>
       <c r="N77">
-        <v>2.388250000000001</v>
+        <v>-0.7009167999999999</v>
       </c>
       <c r="O77">
-        <v>0.2388250000000001</v>
+        <v>-0.07009167999999999</v>
       </c>
       <c r="P77">
-        <v>2.149425000000001</v>
+        <v>-0.6308251199999999</v>
       </c>
       <c r="Q77">
-        <v>2.869425000000001</v>
+        <v>0.08917488000000007</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2831330081114489</v>
+        <v>0.2945750196802951</v>
       </c>
       <c r="T77">
-        <v>3.671466154542664</v>
+        <v>3.848470434516975</v>
       </c>
       <c r="U77">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.1</v>
+        <v>0.09103792026019253</v>
       </c>
       <c r="W77">
-        <v>0.081</v>
+        <v>0.1334356333058037</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y77">
-        <v>1.504728694457653</v>
+        <v>0.9103792026019252</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7769,22 +7769,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1721090860356816</v>
+        <v>0.1731190860356817</v>
       </c>
       <c r="C78">
-        <v>-11.60417458325575</v>
+        <v>-12.5749604161976</v>
       </c>
       <c r="D78">
-        <v>38.07182541674425</v>
+        <v>37.8020395838024</v>
       </c>
       <c r="E78">
-        <v>39.776</v>
+        <v>40.477</v>
       </c>
       <c r="F78">
-        <v>53.276</v>
+        <v>53.977</v>
       </c>
       <c r="G78">
         <v>3.6</v>
@@ -7805,37 +7805,37 @@
         <v>7.12</v>
       </c>
       <c r="M78">
-        <v>7.8209168</v>
+        <v>7.9238236</v>
       </c>
       <c r="N78">
-        <v>-0.7009167999999999</v>
+        <v>-0.8038236000000003</v>
       </c>
       <c r="O78">
-        <v>-0.07009167999999999</v>
+        <v>-0.08038236000000004</v>
       </c>
       <c r="P78">
-        <v>-0.6308251199999999</v>
+        <v>-0.7234412400000003</v>
       </c>
       <c r="Q78">
-        <v>0.08917488000000007</v>
+        <v>-0.003441240000000345</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2945750196802951</v>
+        <v>0.3053913248837862</v>
       </c>
       <c r="T78">
-        <v>3.848470434516975</v>
+        <v>4.015795236017713</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.09103792026019253</v>
+        <v>0.08985560960746275</v>
       </c>
       <c r="W78">
-        <v>0.1334356333058037</v>
+        <v>0.1336091965096245</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.9103792026019252</v>
+        <v>0.8985560960746274</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7851,22 +7851,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1731190860356817</v>
+        <v>0.1741290860356817</v>
       </c>
       <c r="C79">
-        <v>-12.5749604161976</v>
+        <v>-13.54194962227459</v>
       </c>
       <c r="D79">
-        <v>37.8020395838024</v>
+        <v>37.53605037772541</v>
       </c>
       <c r="E79">
-        <v>40.477</v>
+        <v>41.178</v>
       </c>
       <c r="F79">
-        <v>53.977</v>
+        <v>54.678</v>
       </c>
       <c r="G79">
         <v>3.6</v>
@@ -7887,37 +7887,37 @@
         <v>7.12</v>
       </c>
       <c r="M79">
-        <v>7.9238236</v>
+        <v>8.0267304</v>
       </c>
       <c r="N79">
-        <v>-0.8038236000000003</v>
+        <v>-0.9067303999999998</v>
       </c>
       <c r="O79">
-        <v>-0.08038236000000004</v>
+        <v>-0.09067303999999998</v>
       </c>
       <c r="P79">
-        <v>-0.7234412400000003</v>
+        <v>-0.8160573599999998</v>
       </c>
       <c r="Q79">
-        <v>-0.003441240000000345</v>
+        <v>-0.09605735999999987</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3053913248837862</v>
+        <v>0.3171909305603219</v>
       </c>
       <c r="T79">
-        <v>4.015795236017713</v>
+        <v>4.198331383109427</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.08985560960746275</v>
+        <v>0.08870361461249528</v>
       </c>
       <c r="W79">
-        <v>0.1336091965096245</v>
+        <v>0.1337783093748857</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8985560960746274</v>
+        <v>0.8870361461249527</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7933,22 +7933,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1741290860356817</v>
+        <v>0.1751390860356817</v>
       </c>
       <c r="C80">
-        <v>-13.54194962227459</v>
+        <v>-14.5052217849428</v>
       </c>
       <c r="D80">
-        <v>37.53605037772541</v>
+        <v>37.2737782150572</v>
       </c>
       <c r="E80">
-        <v>41.178</v>
+        <v>41.879</v>
       </c>
       <c r="F80">
-        <v>54.678</v>
+        <v>55.379</v>
       </c>
       <c r="G80">
         <v>3.6</v>
@@ -7969,37 +7969,37 @@
         <v>7.12</v>
       </c>
       <c r="M80">
-        <v>8.0267304</v>
+        <v>8.129637200000001</v>
       </c>
       <c r="N80">
-        <v>-0.9067303999999998</v>
+        <v>-1.009637200000001</v>
       </c>
       <c r="O80">
-        <v>-0.09067303999999998</v>
+        <v>-0.1009637200000001</v>
       </c>
       <c r="P80">
-        <v>-0.8160573599999998</v>
+        <v>-0.908673480000001</v>
       </c>
       <c r="Q80">
-        <v>-0.09605735999999987</v>
+        <v>-0.1886734800000011</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3171909305603219</v>
+        <v>0.3301143082060516</v>
       </c>
       <c r="T80">
-        <v>4.198331383109427</v>
+        <v>4.398251925162257</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.08870361461249528</v>
+        <v>0.08758078404778014</v>
       </c>
       <c r="W80">
-        <v>0.1337783093748857</v>
+        <v>0.1339431409017859</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8870361461249527</v>
+        <v>0.8758078404778012</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8015,22 +8015,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1751390860356817</v>
+        <v>0.1761490860356816</v>
       </c>
       <c r="C81">
-        <v>-14.5052217849428</v>
+        <v>-15.46485427882742</v>
       </c>
       <c r="D81">
-        <v>37.2737782150572</v>
+        <v>37.01514572117257</v>
       </c>
       <c r="E81">
-        <v>41.879</v>
+        <v>42.58</v>
       </c>
       <c r="F81">
-        <v>55.379</v>
+        <v>56.08</v>
       </c>
       <c r="G81">
         <v>3.6</v>
@@ -8051,37 +8051,37 @@
         <v>7.12</v>
       </c>
       <c r="M81">
-        <v>8.129637200000001</v>
+        <v>8.232544000000001</v>
       </c>
       <c r="N81">
-        <v>-1.009637200000001</v>
+        <v>-1.112544000000001</v>
       </c>
       <c r="O81">
-        <v>-0.1009637200000001</v>
+        <v>-0.1112544000000001</v>
       </c>
       <c r="P81">
-        <v>-0.908673480000001</v>
+        <v>-1.001289600000001</v>
       </c>
       <c r="Q81">
-        <v>-0.1886734800000011</v>
+        <v>-0.2812896000000007</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3301143082060516</v>
+        <v>0.3443300236163541</v>
       </c>
       <c r="T81">
-        <v>4.398251925162257</v>
+        <v>4.618164521420369</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.08758078404778014</v>
+        <v>0.08648602424718288</v>
       </c>
       <c r="W81">
-        <v>0.1339431409017859</v>
+        <v>0.1341038516405136</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8758078404778012</v>
+        <v>0.8648602424718288</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8097,22 +8097,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1761490860356816</v>
+        <v>0.1771590860356817</v>
       </c>
       <c r="C82">
-        <v>-15.46485427882742</v>
+        <v>-16.42092234582717</v>
       </c>
       <c r="D82">
-        <v>37.01514572117257</v>
+        <v>36.76007765417283</v>
       </c>
       <c r="E82">
-        <v>42.58</v>
+        <v>43.281</v>
       </c>
       <c r="F82">
-        <v>56.08</v>
+        <v>56.781</v>
       </c>
       <c r="G82">
         <v>3.6</v>
@@ -8133,37 +8133,37 @@
         <v>7.12</v>
       </c>
       <c r="M82">
-        <v>8.232544000000001</v>
+        <v>8.3354508</v>
       </c>
       <c r="N82">
-        <v>-1.112544000000001</v>
+        <v>-1.2154508</v>
       </c>
       <c r="O82">
-        <v>-0.1112544000000001</v>
+        <v>-0.12154508</v>
       </c>
       <c r="P82">
-        <v>-1.001289600000001</v>
+        <v>-1.09390572</v>
       </c>
       <c r="Q82">
-        <v>-0.2812896000000007</v>
+        <v>-0.3739057200000002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3443300236163541</v>
+        <v>0.360042130122478</v>
       </c>
       <c r="T82">
-        <v>4.618164521420369</v>
+        <v>4.861225812021442</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.08648602424718288</v>
+        <v>0.08541829555277322</v>
       </c>
       <c r="W82">
-        <v>0.1341038516405136</v>
+        <v>0.1342605942128529</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8648602424718288</v>
+        <v>0.8541829555277323</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8179,22 +8179,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1771590860356817</v>
+        <v>0.1781690860356817</v>
       </c>
       <c r="C83">
-        <v>-16.42092234582717</v>
+        <v>-17.37349916809338</v>
       </c>
       <c r="D83">
-        <v>36.76007765417283</v>
+        <v>36.50850083190662</v>
       </c>
       <c r="E83">
-        <v>43.281</v>
+        <v>43.982</v>
       </c>
       <c r="F83">
-        <v>56.781</v>
+        <v>57.482</v>
       </c>
       <c r="G83">
         <v>3.6</v>
@@ -8215,37 +8215,37 @@
         <v>7.12</v>
       </c>
       <c r="M83">
-        <v>8.3354508</v>
+        <v>8.438357600000002</v>
       </c>
       <c r="N83">
-        <v>-1.2154508</v>
+        <v>-1.318357600000001</v>
       </c>
       <c r="O83">
-        <v>-0.12154508</v>
+        <v>-0.1318357600000002</v>
       </c>
       <c r="P83">
-        <v>-1.09390572</v>
+        <v>-1.186521840000001</v>
       </c>
       <c r="Q83">
-        <v>-0.3739057200000002</v>
+        <v>-0.4665218400000013</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.360042130122478</v>
+        <v>0.3775000262403935</v>
       </c>
       <c r="T83">
-        <v>4.861225812021442</v>
+        <v>5.1312939126893</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.08541829555277322</v>
+        <v>0.08437660902164183</v>
       </c>
       <c r="W83">
-        <v>0.1342605942128529</v>
+        <v>0.134413513795623</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8541829555277323</v>
+        <v>0.8437660902164182</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8261,22 +8261,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1781690860356817</v>
+        <v>0.1791790860356817</v>
       </c>
       <c r="C84">
-        <v>-17.37349916809338</v>
+        <v>-18.32265593803299</v>
       </c>
       <c r="D84">
-        <v>36.50850083190662</v>
+        <v>36.26034406196701</v>
       </c>
       <c r="E84">
-        <v>43.982</v>
+        <v>44.683</v>
       </c>
       <c r="F84">
-        <v>57.482</v>
+        <v>58.183</v>
       </c>
       <c r="G84">
         <v>3.6</v>
@@ -8297,37 +8297,37 @@
         <v>7.12</v>
       </c>
       <c r="M84">
-        <v>8.438357600000002</v>
+        <v>8.541264400000001</v>
       </c>
       <c r="N84">
-        <v>-1.318357600000001</v>
+        <v>-1.421264400000001</v>
       </c>
       <c r="O84">
-        <v>-0.1318357600000002</v>
+        <v>-0.1421264400000001</v>
       </c>
       <c r="P84">
-        <v>-1.186521840000001</v>
+        <v>-1.279137960000001</v>
       </c>
       <c r="Q84">
-        <v>-0.4665218400000013</v>
+        <v>-0.5591379600000008</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3775000262403935</v>
+        <v>0.3970117924898284</v>
       </c>
       <c r="T84">
-        <v>5.1312939126893</v>
+        <v>5.433134731082789</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.08437660902164183</v>
+        <v>0.08336002337077869</v>
       </c>
       <c r="W84">
-        <v>0.134413513795623</v>
+        <v>0.1345627485691697</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8437660902164182</v>
+        <v>0.8336002337077868</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8343,22 +8343,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1791790860356817</v>
+        <v>0.1801890860356817</v>
       </c>
       <c r="C85">
-        <v>-18.32265593803299</v>
+        <v>-19.26846192547579</v>
       </c>
       <c r="D85">
-        <v>36.26034406196701</v>
+        <v>36.01553807452421</v>
       </c>
       <c r="E85">
-        <v>44.683</v>
+        <v>45.384</v>
       </c>
       <c r="F85">
-        <v>58.183</v>
+        <v>58.884</v>
       </c>
       <c r="G85">
         <v>3.6</v>
@@ -8379,37 +8379,37 @@
         <v>7.12</v>
       </c>
       <c r="M85">
-        <v>8.541264400000001</v>
+        <v>8.644171200000001</v>
       </c>
       <c r="N85">
-        <v>-1.421264400000001</v>
+        <v>-1.524171200000001</v>
       </c>
       <c r="O85">
-        <v>-0.1421264400000001</v>
+        <v>-0.1524171200000001</v>
       </c>
       <c r="P85">
-        <v>-1.279137960000001</v>
+        <v>-1.371754080000001</v>
       </c>
       <c r="Q85">
-        <v>-0.5591379600000008</v>
+        <v>-0.6517540800000006</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3970117924898284</v>
+        <v>0.4189625295204428</v>
       </c>
       <c r="T85">
-        <v>5.433134731082789</v>
+        <v>5.772705651775465</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.08336002337077869</v>
+        <v>0.08236764214017418</v>
       </c>
       <c r="W85">
-        <v>0.1345627485691697</v>
+        <v>0.1347084301338224</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8336002337077868</v>
+        <v>0.8236764214017418</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8425,22 +8425,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1801890860356817</v>
+        <v>0.1811990860356816</v>
       </c>
       <c r="C86">
-        <v>-19.26846192547578</v>
+        <v>-20.210984542139</v>
       </c>
       <c r="D86">
-        <v>36.01553807452421</v>
+        <v>35.77401545786099</v>
       </c>
       <c r="E86">
-        <v>45.38399999999999</v>
+        <v>46.08499999999999</v>
       </c>
       <c r="F86">
-        <v>58.88399999999999</v>
+        <v>59.58499999999999</v>
       </c>
       <c r="G86">
         <v>3.6</v>
@@ -8461,37 +8461,37 @@
         <v>7.12</v>
       </c>
       <c r="M86">
-        <v>8.644171200000001</v>
+        <v>8.747078</v>
       </c>
       <c r="N86">
-        <v>-1.524171200000001</v>
+        <v>-1.627078</v>
       </c>
       <c r="O86">
-        <v>-0.1524171200000001</v>
+        <v>-0.1627078</v>
       </c>
       <c r="P86">
-        <v>-1.371754080000001</v>
+        <v>-1.4643702</v>
       </c>
       <c r="Q86">
-        <v>-0.6517540800000006</v>
+        <v>-0.7443702000000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4189625295204426</v>
+        <v>0.443840031488472</v>
       </c>
       <c r="T86">
-        <v>5.77270565177546</v>
+        <v>6.157552695227158</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.08236764214017418</v>
+        <v>0.08139861105617213</v>
       </c>
       <c r="W86">
-        <v>0.1347084301338224</v>
+        <v>0.1348506838969539</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8236764214017418</v>
+        <v>0.8139861105617213</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8507,22 +8507,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1811990860356816</v>
+        <v>0.1822090860356817</v>
       </c>
       <c r="C87">
-        <v>-20.210984542139</v>
+        <v>-21.15028940351554</v>
       </c>
       <c r="D87">
-        <v>35.77401545786099</v>
+        <v>35.53571059648445</v>
       </c>
       <c r="E87">
-        <v>46.08499999999999</v>
+        <v>46.78599999999999</v>
       </c>
       <c r="F87">
-        <v>59.58499999999999</v>
+        <v>60.28599999999999</v>
       </c>
       <c r="G87">
         <v>3.6</v>
@@ -8543,37 +8543,37 @@
         <v>7.12</v>
       </c>
       <c r="M87">
-        <v>8.747078</v>
+        <v>8.8499848</v>
       </c>
       <c r="N87">
-        <v>-1.627078</v>
+        <v>-1.7299848</v>
       </c>
       <c r="O87">
-        <v>-0.1627078</v>
+        <v>-0.17299848</v>
       </c>
       <c r="P87">
-        <v>-1.4643702</v>
+        <v>-1.55698632</v>
       </c>
       <c r="Q87">
-        <v>-0.7443702000000001</v>
+        <v>-0.8369863199999996</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.443840031488472</v>
+        <v>0.4722714623090772</v>
       </c>
       <c r="T87">
-        <v>6.157552695227158</v>
+        <v>6.597377887743384</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.08139861105617213</v>
+        <v>0.0804521155787748</v>
       </c>
       <c r="W87">
-        <v>0.1348506838969539</v>
+        <v>0.1349896294330359</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8139861105617213</v>
+        <v>0.8045211557877479</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8589,22 +8589,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1822090860356817</v>
+        <v>0.2313925859472634</v>
       </c>
       <c r="C88">
-        <v>-21.15028940351554</v>
+        <v>-30.55517963973977</v>
       </c>
       <c r="D88">
-        <v>35.53571059648445</v>
+        <v>26.83182036026022</v>
       </c>
       <c r="E88">
-        <v>46.78599999999999</v>
+        <v>47.48699999999999</v>
       </c>
       <c r="F88">
-        <v>60.28599999999999</v>
+        <v>60.98699999999999</v>
       </c>
       <c r="G88">
         <v>3.6</v>
@@ -8625,45 +8625,45 @@
         <v>7.12</v>
       </c>
       <c r="M88">
-        <v>8.8499848</v>
+        <v>12.2461896</v>
       </c>
       <c r="N88">
-        <v>-1.7299848</v>
+        <v>-5.126189599999999</v>
       </c>
       <c r="O88">
-        <v>-0.17299848</v>
+        <v>-0.51261896</v>
       </c>
       <c r="P88">
-        <v>-1.55698632</v>
+        <v>-4.613570639999999</v>
       </c>
       <c r="Q88">
-        <v>-0.8369863199999996</v>
+        <v>-3.893570639999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4722714623090772</v>
+        <v>0.5142577279604038</v>
       </c>
       <c r="T88">
-        <v>6.597377887743384</v>
+        <v>7.246892064136813</v>
       </c>
       <c r="U88">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.0804521155787748</v>
+        <v>0.05814053377060241</v>
       </c>
       <c r="W88">
-        <v>0.1349896294330359</v>
+        <v>0.189125380818863</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.8045211557877479</v>
+        <v>0.5814053377060242</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8671,22 +8671,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2313925859472634</v>
+        <v>0.2329425859472634</v>
       </c>
       <c r="C89">
-        <v>-30.55517963973977</v>
+        <v>-31.46170781329678</v>
       </c>
       <c r="D89">
-        <v>26.83182036026022</v>
+        <v>26.62629218670322</v>
       </c>
       <c r="E89">
-        <v>47.48699999999999</v>
+        <v>48.188</v>
       </c>
       <c r="F89">
-        <v>60.98699999999999</v>
+        <v>61.688</v>
       </c>
       <c r="G89">
         <v>3.6</v>
@@ -8707,37 +8707,37 @@
         <v>7.12</v>
       </c>
       <c r="M89">
-        <v>12.2461896</v>
+        <v>12.3869504</v>
       </c>
       <c r="N89">
-        <v>-5.126189599999999</v>
+        <v>-5.2669504</v>
       </c>
       <c r="O89">
-        <v>-0.51261896</v>
+        <v>-0.52669504</v>
       </c>
       <c r="P89">
-        <v>-4.613570639999999</v>
+        <v>-4.74025536</v>
       </c>
       <c r="Q89">
-        <v>-3.893570639999999</v>
+        <v>-4.02025536</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5142577279604038</v>
+        <v>0.5532958719571043</v>
       </c>
       <c r="T89">
-        <v>7.246892064136813</v>
+        <v>7.850799736148216</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.05814053377060241</v>
+        <v>0.05747984588684556</v>
       </c>
       <c r="W89">
-        <v>0.189125380818863</v>
+        <v>0.1892580469459214</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5814053377060242</v>
+        <v>0.5747984588684556</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8753,22 +8753,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2329425859472634</v>
+        <v>0.2344925859472634</v>
       </c>
       <c r="C90">
-        <v>-31.46170781329678</v>
+        <v>-32.36511128473494</v>
       </c>
       <c r="D90">
-        <v>26.62629218670322</v>
+        <v>26.42388871526506</v>
       </c>
       <c r="E90">
-        <v>48.188</v>
+        <v>48.889</v>
       </c>
       <c r="F90">
-        <v>61.688</v>
+        <v>62.389</v>
       </c>
       <c r="G90">
         <v>3.6</v>
@@ -8789,37 +8789,37 @@
         <v>7.12</v>
       </c>
       <c r="M90">
-        <v>12.3869504</v>
+        <v>12.5277112</v>
       </c>
       <c r="N90">
-        <v>-5.2669504</v>
+        <v>-5.407711199999999</v>
       </c>
       <c r="O90">
-        <v>-0.52669504</v>
+        <v>-0.5407711199999999</v>
       </c>
       <c r="P90">
-        <v>-4.74025536</v>
+        <v>-4.866940079999999</v>
       </c>
       <c r="Q90">
-        <v>-4.02025536</v>
+        <v>-4.146940079999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5532958719571043</v>
+        <v>0.5994318603168409</v>
       </c>
       <c r="T90">
-        <v>7.850799736148216</v>
+        <v>8.564508803070781</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.05747984588684556</v>
+        <v>0.05683400492182483</v>
       </c>
       <c r="W90">
-        <v>0.1892580469459214</v>
+        <v>0.1893877318116976</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5747984588684556</v>
+        <v>0.5683400492182483</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8835,22 +8835,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2344925859472634</v>
+        <v>0.2360425859472634</v>
       </c>
       <c r="C91">
-        <v>-32.36511128473494</v>
+        <v>-33.26546077503497</v>
       </c>
       <c r="D91">
-        <v>26.42388871526506</v>
+        <v>26.22453922496502</v>
       </c>
       <c r="E91">
-        <v>48.889</v>
+        <v>49.59</v>
       </c>
       <c r="F91">
-        <v>62.389</v>
+        <v>63.09</v>
       </c>
       <c r="G91">
         <v>3.6</v>
@@ -8871,37 +8871,37 @@
         <v>7.12</v>
       </c>
       <c r="M91">
-        <v>12.5277112</v>
+        <v>12.668472</v>
       </c>
       <c r="N91">
-        <v>-5.407711199999999</v>
+        <v>-5.548471999999999</v>
       </c>
       <c r="O91">
-        <v>-0.5407711199999999</v>
+        <v>-0.5548472</v>
       </c>
       <c r="P91">
-        <v>-4.866940079999999</v>
+        <v>-4.993624799999999</v>
       </c>
       <c r="Q91">
-        <v>-4.146940079999999</v>
+        <v>-4.273624799999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5994318603168409</v>
+        <v>0.6547950463485251</v>
       </c>
       <c r="T91">
-        <v>8.564508803070781</v>
+        <v>9.420959683377861</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.05683400492182483</v>
+        <v>0.056202515978249</v>
       </c>
       <c r="W91">
-        <v>0.1893877318116976</v>
+        <v>0.1895145347915676</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5683400492182483</v>
+        <v>0.5620251597824899</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8917,22 +8917,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2360425859472634</v>
+        <v>0.2375925859472633</v>
       </c>
       <c r="C92">
-        <v>-33.26546077503497</v>
+        <v>-34.16282488699929</v>
       </c>
       <c r="D92">
-        <v>26.22453922496502</v>
+        <v>26.0281751130007</v>
       </c>
       <c r="E92">
-        <v>49.59</v>
+        <v>50.291</v>
       </c>
       <c r="F92">
-        <v>63.09</v>
+        <v>63.791</v>
       </c>
       <c r="G92">
         <v>3.6</v>
@@ -8953,37 +8953,37 @@
         <v>7.12</v>
       </c>
       <c r="M92">
-        <v>12.668472</v>
+        <v>12.8092328</v>
       </c>
       <c r="N92">
-        <v>-5.548471999999999</v>
+        <v>-5.6892328</v>
       </c>
       <c r="O92">
-        <v>-0.5548472</v>
+        <v>-0.56892328</v>
       </c>
       <c r="P92">
-        <v>-4.993624799999999</v>
+        <v>-5.12030952</v>
       </c>
       <c r="Q92">
-        <v>-4.273624799999999</v>
+        <v>-4.40030952</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6547950463485251</v>
+        <v>0.7224611626094725</v>
       </c>
       <c r="T92">
-        <v>9.420959683377861</v>
+        <v>10.46773298153096</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.056202515978249</v>
+        <v>0.05558490591255395</v>
       </c>
       <c r="W92">
-        <v>0.1895145347915676</v>
+        <v>0.1896385508927592</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5620251597824899</v>
+        <v>0.5558490591255395</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8999,22 +8999,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2375925859472633</v>
+        <v>0.2391425859472634</v>
       </c>
       <c r="C93">
-        <v>-34.16282488699929</v>
+        <v>-35.05727018396506</v>
       </c>
       <c r="D93">
-        <v>26.0281751130007</v>
+        <v>25.83472981603494</v>
       </c>
       <c r="E93">
-        <v>50.291</v>
+        <v>50.992</v>
       </c>
       <c r="F93">
-        <v>63.791</v>
+        <v>64.492</v>
       </c>
       <c r="G93">
         <v>3.6</v>
@@ -9035,37 +9035,37 @@
         <v>7.12</v>
       </c>
       <c r="M93">
-        <v>12.8092328</v>
+        <v>12.9499936</v>
       </c>
       <c r="N93">
-        <v>-5.6892328</v>
+        <v>-5.829993600000001</v>
       </c>
       <c r="O93">
-        <v>-0.56892328</v>
+        <v>-0.5829993600000001</v>
       </c>
       <c r="P93">
-        <v>-5.12030952</v>
+        <v>-5.246994240000001</v>
       </c>
       <c r="Q93">
-        <v>-4.40030952</v>
+        <v>-4.526994240000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7224611626094725</v>
+        <v>0.8070438079356567</v>
       </c>
       <c r="T93">
-        <v>10.46773298153096</v>
+        <v>11.77619960422233</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.05558490591255395</v>
+        <v>0.05498072215263489</v>
       </c>
       <c r="W93">
-        <v>0.1896385508927592</v>
+        <v>0.1897598709917509</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5558490591255395</v>
+        <v>0.5498072215263488</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9081,22 +9081,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2391425859472634</v>
+        <v>0.2406925859472633</v>
       </c>
       <c r="C94">
-        <v>-35.05727018396506</v>
+        <v>-35.94886126503316</v>
       </c>
       <c r="D94">
-        <v>25.83472981603494</v>
+        <v>25.64413873496684</v>
       </c>
       <c r="E94">
-        <v>50.992</v>
+        <v>51.693</v>
       </c>
       <c r="F94">
-        <v>64.492</v>
+        <v>65.193</v>
       </c>
       <c r="G94">
         <v>3.6</v>
@@ -9117,37 +9117,37 @@
         <v>7.12</v>
       </c>
       <c r="M94">
-        <v>12.9499936</v>
+        <v>13.0907544</v>
       </c>
       <c r="N94">
-        <v>-5.829993600000001</v>
+        <v>-5.9707544</v>
       </c>
       <c r="O94">
-        <v>-0.5829993600000001</v>
+        <v>-0.59707544</v>
       </c>
       <c r="P94">
-        <v>-5.246994240000001</v>
+        <v>-5.373678959999999</v>
       </c>
       <c r="Q94">
-        <v>-4.526994240000001</v>
+        <v>-4.65367896</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8070438079356567</v>
+        <v>0.9157929233550363</v>
       </c>
       <c r="T94">
-        <v>11.77619960422233</v>
+        <v>13.45851383339695</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.05498072215263489</v>
+        <v>0.05438953159185387</v>
       </c>
       <c r="W94">
-        <v>0.1897598709917509</v>
+        <v>0.1898785820563557</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5498072215263488</v>
+        <v>0.5438953159185387</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9163,22 +9163,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2406925859472633</v>
+        <v>0.2422425859472633</v>
       </c>
       <c r="C95">
-        <v>-35.94886126503316</v>
+        <v>-36.83766083699165</v>
       </c>
       <c r="D95">
-        <v>25.64413873496684</v>
+        <v>25.45633916300836</v>
       </c>
       <c r="E95">
-        <v>51.693</v>
+        <v>52.39400000000001</v>
       </c>
       <c r="F95">
-        <v>65.193</v>
+        <v>65.89400000000001</v>
       </c>
       <c r="G95">
         <v>3.6</v>
@@ -9199,37 +9199,37 @@
         <v>7.12</v>
       </c>
       <c r="M95">
-        <v>13.0907544</v>
+        <v>13.2315152</v>
       </c>
       <c r="N95">
-        <v>-5.9707544</v>
+        <v>-6.111515200000002</v>
       </c>
       <c r="O95">
-        <v>-0.59707544</v>
+        <v>-0.6111515200000003</v>
       </c>
       <c r="P95">
-        <v>-5.373678959999999</v>
+        <v>-5.500363680000002</v>
       </c>
       <c r="Q95">
-        <v>-4.65367896</v>
+        <v>-4.780363680000002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9157929233550363</v>
+        <v>1.060791743914209</v>
       </c>
       <c r="T95">
-        <v>13.45851383339695</v>
+        <v>15.70159947229645</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.05438953159185387</v>
+        <v>0.05381091955364264</v>
       </c>
       <c r="W95">
-        <v>0.1898785820563557</v>
+        <v>0.1899947673536286</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5438953159185387</v>
+        <v>0.5381091955364264</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9245,22 +9245,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2422425859472633</v>
+        <v>0.2437925859472634</v>
       </c>
       <c r="C96">
-        <v>-36.83766083699165</v>
+        <v>-37.7237297831017</v>
       </c>
       <c r="D96">
-        <v>25.45633916300836</v>
+        <v>25.27127021689829</v>
       </c>
       <c r="E96">
-        <v>52.39400000000001</v>
+        <v>53.095</v>
       </c>
       <c r="F96">
-        <v>65.89400000000001</v>
+        <v>66.595</v>
       </c>
       <c r="G96">
         <v>3.6</v>
@@ -9281,37 +9281,37 @@
         <v>7.12</v>
       </c>
       <c r="M96">
-        <v>13.2315152</v>
+        <v>13.372276</v>
       </c>
       <c r="N96">
-        <v>-6.111515200000002</v>
+        <v>-6.252275999999999</v>
       </c>
       <c r="O96">
-        <v>-0.6111515200000003</v>
+        <v>-0.6252276</v>
       </c>
       <c r="P96">
-        <v>-5.500363680000002</v>
+        <v>-5.6270484</v>
       </c>
       <c r="Q96">
-        <v>-4.780363680000002</v>
+        <v>-4.9070484</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.060791743914209</v>
+        <v>1.263790092697052</v>
       </c>
       <c r="T96">
-        <v>15.70159947229645</v>
+        <v>18.84191936675574</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.05381091955364264</v>
+        <v>0.05324448882149905</v>
       </c>
       <c r="W96">
-        <v>0.1899947673536286</v>
+        <v>0.190108506644643</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5381091955364264</v>
+        <v>0.5324448882149906</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9327,22 +9327,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2437925859472634</v>
+        <v>0.2453425859472634</v>
       </c>
       <c r="C97">
-        <v>-37.7237297831017</v>
+        <v>-38.60712722890504</v>
       </c>
       <c r="D97">
-        <v>25.27127021689829</v>
+        <v>25.08887277109497</v>
       </c>
       <c r="E97">
-        <v>53.095</v>
+        <v>53.79600000000001</v>
       </c>
       <c r="F97">
-        <v>66.595</v>
+        <v>67.29600000000001</v>
       </c>
       <c r="G97">
         <v>3.6</v>
@@ -9363,37 +9363,37 @@
         <v>7.12</v>
       </c>
       <c r="M97">
-        <v>13.372276</v>
+        <v>13.5130368</v>
       </c>
       <c r="N97">
-        <v>-6.252275999999999</v>
+        <v>-6.393036800000002</v>
       </c>
       <c r="O97">
-        <v>-0.6252276</v>
+        <v>-0.6393036800000003</v>
       </c>
       <c r="P97">
-        <v>-5.6270484</v>
+        <v>-5.753733120000001</v>
       </c>
       <c r="Q97">
-        <v>-4.9070484</v>
+        <v>-5.033733120000002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.263790092697052</v>
+        <v>1.568287615871315</v>
       </c>
       <c r="T97">
-        <v>18.84191936675574</v>
+        <v>23.55239920844469</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.05324448882149905</v>
+        <v>0.05268985872960844</v>
       </c>
       <c r="W97">
-        <v>0.190108506644643</v>
+        <v>0.1902198763670946</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5324448882149906</v>
+        <v>0.5268985872960843</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9409,22 +9409,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2453425859472634</v>
+        <v>0.2468925859472633</v>
       </c>
       <c r="C98">
-        <v>-38.60712722890503</v>
+        <v>-39.48791060520162</v>
       </c>
       <c r="D98">
-        <v>25.08887277109497</v>
+        <v>24.90908939479836</v>
       </c>
       <c r="E98">
-        <v>53.79599999999999</v>
+        <v>54.49699999999999</v>
       </c>
       <c r="F98">
-        <v>67.29599999999999</v>
+        <v>67.99699999999999</v>
       </c>
       <c r="G98">
         <v>3.6</v>
@@ -9445,37 +9445,37 @@
         <v>7.12</v>
       </c>
       <c r="M98">
-        <v>13.5130368</v>
+        <v>13.6537976</v>
       </c>
       <c r="N98">
-        <v>-6.393036799999998</v>
+        <v>-6.533797599999997</v>
       </c>
       <c r="O98">
-        <v>-0.6393036799999998</v>
+        <v>-0.6533797599999998</v>
       </c>
       <c r="P98">
-        <v>-5.753733119999998</v>
+        <v>-5.880417839999997</v>
       </c>
       <c r="Q98">
-        <v>-5.033733119999998</v>
+        <v>-5.160417839999997</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.568287615871312</v>
+        <v>2.075783487828415</v>
       </c>
       <c r="T98">
-        <v>23.55239920844463</v>
+        <v>31.40319894459284</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.05268985872960844</v>
+        <v>0.05214666430971557</v>
       </c>
       <c r="W98">
-        <v>0.1902198763670946</v>
+        <v>0.1903289498066091</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5268985872960844</v>
+        <v>0.5214666430971557</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9491,22 +9491,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2468925859472633</v>
+        <v>0.2484425859472634</v>
       </c>
       <c r="C99">
-        <v>-39.48791060520162</v>
+        <v>-40.36613570833927</v>
       </c>
       <c r="D99">
-        <v>24.90908939479836</v>
+        <v>24.73186429166072</v>
       </c>
       <c r="E99">
-        <v>54.49699999999999</v>
+        <v>55.19799999999999</v>
       </c>
       <c r="F99">
-        <v>67.99699999999999</v>
+        <v>68.69799999999999</v>
       </c>
       <c r="G99">
         <v>3.6</v>
@@ -9527,37 +9527,37 @@
         <v>7.12</v>
       </c>
       <c r="M99">
-        <v>13.6537976</v>
+        <v>13.7945584</v>
       </c>
       <c r="N99">
-        <v>-6.533797599999997</v>
+        <v>-6.6745584</v>
       </c>
       <c r="O99">
-        <v>-0.6533797599999998</v>
+        <v>-0.66745584</v>
       </c>
       <c r="P99">
-        <v>-5.880417839999997</v>
+        <v>-6.00710256</v>
       </c>
       <c r="Q99">
-        <v>-5.160417839999997</v>
+        <v>-5.28710256</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.075783487828415</v>
+        <v>3.090775231742623</v>
       </c>
       <c r="T99">
-        <v>31.40319894459284</v>
+        <v>47.10479841688926</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.05214666430971557</v>
+        <v>0.05161455549022868</v>
       </c>
       <c r="W99">
-        <v>0.1903289498066091</v>
+        <v>0.1904357972575621</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5214666430971557</v>
+        <v>0.5161455549022866</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9573,22 +9573,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2484425859472634</v>
+        <v>0.2499925859472633</v>
       </c>
       <c r="C100">
-        <v>-40.36613570833927</v>
+        <v>-41.24185675794725</v>
       </c>
       <c r="D100">
-        <v>24.73186429166072</v>
+        <v>24.55714324205273</v>
       </c>
       <c r="E100">
-        <v>55.19799999999999</v>
+        <v>55.89899999999999</v>
       </c>
       <c r="F100">
-        <v>68.69799999999999</v>
+        <v>69.39899999999999</v>
       </c>
       <c r="G100">
         <v>3.6</v>
@@ -9609,37 +9609,37 @@
         <v>7.12</v>
       </c>
       <c r="M100">
-        <v>13.7945584</v>
+        <v>13.9353192</v>
       </c>
       <c r="N100">
-        <v>-6.6745584</v>
+        <v>-6.815319199999998</v>
       </c>
       <c r="O100">
-        <v>-0.66745584</v>
+        <v>-0.6815319199999998</v>
       </c>
       <c r="P100">
-        <v>-6.00710256</v>
+        <v>-6.133787279999998</v>
       </c>
       <c r="Q100">
-        <v>-5.28710256</v>
+        <v>-5.413787279999998</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.090775231742623</v>
+        <v>6.135750463485246</v>
       </c>
       <c r="T100">
-        <v>47.10479841688926</v>
+        <v>94.20959683377851</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.05161455549022868</v>
+        <v>0.05109319634386272</v>
       </c>
       <c r="W100">
-        <v>0.1904357972575621</v>
+        <v>0.1905404861741524</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9647,91 +9647,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5161455549022866</v>
+        <v>0.5109319634386273</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2499925859472633</v>
-      </c>
-      <c r="C101">
-        <v>-41.24185675794725</v>
-      </c>
-      <c r="D101">
-        <v>24.55714324205273</v>
-      </c>
-      <c r="E101">
-        <v>55.89899999999999</v>
-      </c>
-      <c r="F101">
-        <v>69.39899999999999</v>
-      </c>
-      <c r="G101">
-        <v>3.6</v>
-      </c>
-      <c r="H101">
-        <v>56.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>7.84</v>
-      </c>
-      <c r="K101">
-        <v>0.72</v>
-      </c>
-      <c r="L101">
-        <v>7.12</v>
-      </c>
-      <c r="M101">
-        <v>13.9353192</v>
-      </c>
-      <c r="N101">
-        <v>-6.815319199999998</v>
-      </c>
-      <c r="O101">
-        <v>-0.6815319199999998</v>
-      </c>
-      <c r="P101">
-        <v>-6.133787279999998</v>
-      </c>
-      <c r="Q101">
-        <v>-5.413787279999998</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.135750463485246</v>
-      </c>
-      <c r="T101">
-        <v>94.20959683377851</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.05109319634386272</v>
-      </c>
-      <c r="W101">
-        <v>0.1905404861741524</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5109319634386273</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
